--- a/solver_data/sudoku data.xlsx
+++ b/solver_data/sudoku data.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jacob w\Desktop\Sudoku Research\Sudoku-solving-bot\solve_data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{0BBA79FC-2D65-4ED6-92AF-46C9543A8EA8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B953A2C5-4132-4A19-8520-F09CE703FB81}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{D8681240-95B1-4340-8AF1-AF0009C365C3}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="384" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="390" uniqueCount="33">
   <si>
     <t>Board #1</t>
   </si>
@@ -156,12 +156,18 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="1"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -176,11 +182,14 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -7351,6 +7360,2045 @@
 </c:chartSpace>
 </file>
 
+<file path=xl/charts/chart8.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US"/>
+              <a:t>Hard</a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="en-US" baseline="0"/>
+              <a:t> board</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:scatterChart>
+        <c:scatterStyle val="lineMarker"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:spPr>
+            <a:ln w="38100" cap="rnd">
+              <a:noFill/>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>Sheet1!$AE$5:$AE$123</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="119"/>
+                <c:pt idx="0">
+                  <c:v>4049</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>4072</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>4053</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>4088</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>4056</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>4036</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>4009</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>4055</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>4093</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>4031</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>4101</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>4069</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>4091</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>4051</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>4075</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>3982</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>3973</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>3962</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>3958</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>3973</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>4053</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>4090</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>4078</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>4052</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>4044</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>3956</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>4306</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>4134</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>4614</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>4276</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>4478</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>4116</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>4206</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>4144</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>4033</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>4155</c:v>
+                </c:pt>
+                <c:pt idx="43">
+                  <c:v>4250</c:v>
+                </c:pt>
+                <c:pt idx="44">
+                  <c:v>4098</c:v>
+                </c:pt>
+                <c:pt idx="45">
+                  <c:v>4242</c:v>
+                </c:pt>
+                <c:pt idx="46">
+                  <c:v>4345</c:v>
+                </c:pt>
+                <c:pt idx="48">
+                  <c:v>4159</c:v>
+                </c:pt>
+                <c:pt idx="49">
+                  <c:v>4111</c:v>
+                </c:pt>
+                <c:pt idx="50">
+                  <c:v>4102</c:v>
+                </c:pt>
+                <c:pt idx="51">
+                  <c:v>4161</c:v>
+                </c:pt>
+                <c:pt idx="52">
+                  <c:v>4168</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>4030</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>4107</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>4126</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>4068</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>4038</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>4220</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>4389</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>4210</c:v>
+                </c:pt>
+                <c:pt idx="63">
+                  <c:v>4331</c:v>
+                </c:pt>
+                <c:pt idx="64">
+                  <c:v>4196</c:v>
+                </c:pt>
+                <c:pt idx="66">
+                  <c:v>4106</c:v>
+                </c:pt>
+                <c:pt idx="67">
+                  <c:v>4161</c:v>
+                </c:pt>
+                <c:pt idx="68">
+                  <c:v>4077</c:v>
+                </c:pt>
+                <c:pt idx="69">
+                  <c:v>4082</c:v>
+                </c:pt>
+                <c:pt idx="70">
+                  <c:v>4078</c:v>
+                </c:pt>
+                <c:pt idx="72">
+                  <c:v>4032</c:v>
+                </c:pt>
+                <c:pt idx="73">
+                  <c:v>4052</c:v>
+                </c:pt>
+                <c:pt idx="74">
+                  <c:v>4055</c:v>
+                </c:pt>
+                <c:pt idx="75">
+                  <c:v>4076</c:v>
+                </c:pt>
+                <c:pt idx="76">
+                  <c:v>4071</c:v>
+                </c:pt>
+                <c:pt idx="78">
+                  <c:v>4209</c:v>
+                </c:pt>
+                <c:pt idx="79">
+                  <c:v>4129</c:v>
+                </c:pt>
+                <c:pt idx="80">
+                  <c:v>4252</c:v>
+                </c:pt>
+                <c:pt idx="81">
+                  <c:v>4356</c:v>
+                </c:pt>
+                <c:pt idx="82">
+                  <c:v>4140</c:v>
+                </c:pt>
+                <c:pt idx="84">
+                  <c:v>4065</c:v>
+                </c:pt>
+                <c:pt idx="85">
+                  <c:v>4045</c:v>
+                </c:pt>
+                <c:pt idx="86">
+                  <c:v>4102</c:v>
+                </c:pt>
+                <c:pt idx="87">
+                  <c:v>4166</c:v>
+                </c:pt>
+                <c:pt idx="88">
+                  <c:v>4188</c:v>
+                </c:pt>
+                <c:pt idx="90">
+                  <c:v>4008</c:v>
+                </c:pt>
+                <c:pt idx="91">
+                  <c:v>3983</c:v>
+                </c:pt>
+                <c:pt idx="92">
+                  <c:v>3973</c:v>
+                </c:pt>
+                <c:pt idx="93">
+                  <c:v>3993</c:v>
+                </c:pt>
+                <c:pt idx="94">
+                  <c:v>3966</c:v>
+                </c:pt>
+                <c:pt idx="96">
+                  <c:v>4052</c:v>
+                </c:pt>
+                <c:pt idx="97">
+                  <c:v>4055</c:v>
+                </c:pt>
+                <c:pt idx="98">
+                  <c:v>4040</c:v>
+                </c:pt>
+                <c:pt idx="99">
+                  <c:v>4038</c:v>
+                </c:pt>
+                <c:pt idx="100">
+                  <c:v>4076</c:v>
+                </c:pt>
+                <c:pt idx="102">
+                  <c:v>3965</c:v>
+                </c:pt>
+                <c:pt idx="103">
+                  <c:v>3966</c:v>
+                </c:pt>
+                <c:pt idx="104">
+                  <c:v>3960</c:v>
+                </c:pt>
+                <c:pt idx="105">
+                  <c:v>3954</c:v>
+                </c:pt>
+                <c:pt idx="106">
+                  <c:v>3990</c:v>
+                </c:pt>
+                <c:pt idx="108">
+                  <c:v>4106</c:v>
+                </c:pt>
+                <c:pt idx="109">
+                  <c:v>4084</c:v>
+                </c:pt>
+                <c:pt idx="110">
+                  <c:v>4006</c:v>
+                </c:pt>
+                <c:pt idx="111">
+                  <c:v>4062</c:v>
+                </c:pt>
+                <c:pt idx="112">
+                  <c:v>4091</c:v>
+                </c:pt>
+                <c:pt idx="114">
+                  <c:v>4031</c:v>
+                </c:pt>
+                <c:pt idx="115">
+                  <c:v>4010</c:v>
+                </c:pt>
+                <c:pt idx="116">
+                  <c:v>4038</c:v>
+                </c:pt>
+                <c:pt idx="117">
+                  <c:v>4031</c:v>
+                </c:pt>
+                <c:pt idx="118">
+                  <c:v>4025</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>Sheet1!$AF$5:$AF$123</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="119"/>
+                <c:pt idx="0">
+                  <c:v>28</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>30</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>28</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>29</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>28</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>28</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>27</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>28</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>30</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>28</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>29</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>28</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>27</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>29</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>27</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>27</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>28</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>30</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>30</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>27</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>29</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>30</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>30</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>28</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>28</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>28</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>28</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>29</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>28</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>29</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>28</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>27</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>29</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>27</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>29</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>26</c:v>
+                </c:pt>
+                <c:pt idx="43">
+                  <c:v>29</c:v>
+                </c:pt>
+                <c:pt idx="44">
+                  <c:v>29</c:v>
+                </c:pt>
+                <c:pt idx="45">
+                  <c:v>30</c:v>
+                </c:pt>
+                <c:pt idx="46">
+                  <c:v>29</c:v>
+                </c:pt>
+                <c:pt idx="48">
+                  <c:v>29</c:v>
+                </c:pt>
+                <c:pt idx="49">
+                  <c:v>27</c:v>
+                </c:pt>
+                <c:pt idx="50">
+                  <c:v>28</c:v>
+                </c:pt>
+                <c:pt idx="51">
+                  <c:v>29</c:v>
+                </c:pt>
+                <c:pt idx="52">
+                  <c:v>28</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>24</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>30</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>26</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>28</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>30</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>30</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>29</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>30</c:v>
+                </c:pt>
+                <c:pt idx="63">
+                  <c:v>29</c:v>
+                </c:pt>
+                <c:pt idx="64">
+                  <c:v>28</c:v>
+                </c:pt>
+                <c:pt idx="66">
+                  <c:v>27</c:v>
+                </c:pt>
+                <c:pt idx="67">
+                  <c:v>28</c:v>
+                </c:pt>
+                <c:pt idx="68">
+                  <c:v>28</c:v>
+                </c:pt>
+                <c:pt idx="69">
+                  <c:v>28</c:v>
+                </c:pt>
+                <c:pt idx="70">
+                  <c:v>26</c:v>
+                </c:pt>
+                <c:pt idx="72">
+                  <c:v>28</c:v>
+                </c:pt>
+                <c:pt idx="73">
+                  <c:v>28</c:v>
+                </c:pt>
+                <c:pt idx="74">
+                  <c:v>28</c:v>
+                </c:pt>
+                <c:pt idx="75">
+                  <c:v>27</c:v>
+                </c:pt>
+                <c:pt idx="76">
+                  <c:v>29</c:v>
+                </c:pt>
+                <c:pt idx="78">
+                  <c:v>29</c:v>
+                </c:pt>
+                <c:pt idx="79">
+                  <c:v>28</c:v>
+                </c:pt>
+                <c:pt idx="80">
+                  <c:v>27</c:v>
+                </c:pt>
+                <c:pt idx="81">
+                  <c:v>28</c:v>
+                </c:pt>
+                <c:pt idx="82">
+                  <c:v>30</c:v>
+                </c:pt>
+                <c:pt idx="84">
+                  <c:v>28</c:v>
+                </c:pt>
+                <c:pt idx="85">
+                  <c:v>29</c:v>
+                </c:pt>
+                <c:pt idx="86">
+                  <c:v>30</c:v>
+                </c:pt>
+                <c:pt idx="87">
+                  <c:v>29</c:v>
+                </c:pt>
+                <c:pt idx="88">
+                  <c:v>28</c:v>
+                </c:pt>
+                <c:pt idx="90">
+                  <c:v>27</c:v>
+                </c:pt>
+                <c:pt idx="91">
+                  <c:v>29</c:v>
+                </c:pt>
+                <c:pt idx="92">
+                  <c:v>29</c:v>
+                </c:pt>
+                <c:pt idx="93">
+                  <c:v>30</c:v>
+                </c:pt>
+                <c:pt idx="94">
+                  <c:v>29</c:v>
+                </c:pt>
+                <c:pt idx="96">
+                  <c:v>28</c:v>
+                </c:pt>
+                <c:pt idx="97">
+                  <c:v>27</c:v>
+                </c:pt>
+                <c:pt idx="98">
+                  <c:v>28</c:v>
+                </c:pt>
+                <c:pt idx="99">
+                  <c:v>29</c:v>
+                </c:pt>
+                <c:pt idx="100">
+                  <c:v>23</c:v>
+                </c:pt>
+                <c:pt idx="102">
+                  <c:v>29</c:v>
+                </c:pt>
+                <c:pt idx="103">
+                  <c:v>29</c:v>
+                </c:pt>
+                <c:pt idx="104">
+                  <c:v>30</c:v>
+                </c:pt>
+                <c:pt idx="105">
+                  <c:v>28</c:v>
+                </c:pt>
+                <c:pt idx="106">
+                  <c:v>27</c:v>
+                </c:pt>
+                <c:pt idx="108">
+                  <c:v>29</c:v>
+                </c:pt>
+                <c:pt idx="109">
+                  <c:v>29</c:v>
+                </c:pt>
+                <c:pt idx="110">
+                  <c:v>28</c:v>
+                </c:pt>
+                <c:pt idx="111">
+                  <c:v>28</c:v>
+                </c:pt>
+                <c:pt idx="112">
+                  <c:v>28</c:v>
+                </c:pt>
+                <c:pt idx="114">
+                  <c:v>28</c:v>
+                </c:pt>
+                <c:pt idx="115">
+                  <c:v>27</c:v>
+                </c:pt>
+                <c:pt idx="116">
+                  <c:v>26</c:v>
+                </c:pt>
+                <c:pt idx="117">
+                  <c:v>29</c:v>
+                </c:pt>
+                <c:pt idx="118">
+                  <c:v>29</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-9E45-42F5-AAA2-A3D32E98BB3C}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:axId val="209826944"/>
+        <c:axId val="209828384"/>
+      </c:scatterChart>
+      <c:valAx>
+        <c:axId val="209826944"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="en-US"/>
+                  <a:t>Time (CPU ticks)</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="209828384"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:valAx>
+        <c:axId val="209828384"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="en-US"/>
+                  <a:t>fitness score</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="209826944"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart9.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US"/>
+              <a:t>17 board</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:scatterChart>
+        <c:scatterStyle val="lineMarker"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:spPr>
+            <a:ln w="38100" cap="rnd">
+              <a:noFill/>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>Sheet1!$AH$5:$AH$123</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="119"/>
+                <c:pt idx="0">
+                  <c:v>3810</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>3765</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>3758</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>3846</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>3852</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>3779</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>3766</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>3813</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>3935</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>3752</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>3738</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>3731</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>3716</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>3735</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>3714</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>3737</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>3762</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>3714</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>3700</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>3720</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>3738</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>3709</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>3692</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>3757</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>3716</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>3724</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>3718</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>3735</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>3774</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>3773</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>3792</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>3761</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>3807</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>3768</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>3751</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>3772</c:v>
+                </c:pt>
+                <c:pt idx="43">
+                  <c:v>3787</c:v>
+                </c:pt>
+                <c:pt idx="44">
+                  <c:v>3750</c:v>
+                </c:pt>
+                <c:pt idx="45">
+                  <c:v>3774</c:v>
+                </c:pt>
+                <c:pt idx="46">
+                  <c:v>3756</c:v>
+                </c:pt>
+                <c:pt idx="48">
+                  <c:v>3812</c:v>
+                </c:pt>
+                <c:pt idx="49">
+                  <c:v>3761</c:v>
+                </c:pt>
+                <c:pt idx="50">
+                  <c:v>3770</c:v>
+                </c:pt>
+                <c:pt idx="51">
+                  <c:v>3778</c:v>
+                </c:pt>
+                <c:pt idx="52">
+                  <c:v>3757</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>3748</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>3770</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>3763</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>3798</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>3771</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>3773</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>3783</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>3774</c:v>
+                </c:pt>
+                <c:pt idx="63">
+                  <c:v>3802</c:v>
+                </c:pt>
+                <c:pt idx="64">
+                  <c:v>3774</c:v>
+                </c:pt>
+                <c:pt idx="66">
+                  <c:v>3751</c:v>
+                </c:pt>
+                <c:pt idx="67">
+                  <c:v>3754</c:v>
+                </c:pt>
+                <c:pt idx="68">
+                  <c:v>3754</c:v>
+                </c:pt>
+                <c:pt idx="69">
+                  <c:v>3796</c:v>
+                </c:pt>
+                <c:pt idx="70">
+                  <c:v>3878</c:v>
+                </c:pt>
+                <c:pt idx="72">
+                  <c:v>3754</c:v>
+                </c:pt>
+                <c:pt idx="73">
+                  <c:v>3750</c:v>
+                </c:pt>
+                <c:pt idx="74">
+                  <c:v>3759</c:v>
+                </c:pt>
+                <c:pt idx="75">
+                  <c:v>4233</c:v>
+                </c:pt>
+                <c:pt idx="76">
+                  <c:v>4450</c:v>
+                </c:pt>
+                <c:pt idx="78">
+                  <c:v>4267</c:v>
+                </c:pt>
+                <c:pt idx="79">
+                  <c:v>4371</c:v>
+                </c:pt>
+                <c:pt idx="80">
+                  <c:v>4456</c:v>
+                </c:pt>
+                <c:pt idx="81">
+                  <c:v>4467</c:v>
+                </c:pt>
+                <c:pt idx="82">
+                  <c:v>4400</c:v>
+                </c:pt>
+                <c:pt idx="84">
+                  <c:v>4528</c:v>
+                </c:pt>
+                <c:pt idx="85">
+                  <c:v>4440</c:v>
+                </c:pt>
+                <c:pt idx="86">
+                  <c:v>4329</c:v>
+                </c:pt>
+                <c:pt idx="87">
+                  <c:v>4317</c:v>
+                </c:pt>
+                <c:pt idx="88">
+                  <c:v>4342</c:v>
+                </c:pt>
+                <c:pt idx="90">
+                  <c:v>4436</c:v>
+                </c:pt>
+                <c:pt idx="91">
+                  <c:v>4419</c:v>
+                </c:pt>
+                <c:pt idx="92">
+                  <c:v>4440</c:v>
+                </c:pt>
+                <c:pt idx="93">
+                  <c:v>4321</c:v>
+                </c:pt>
+                <c:pt idx="94">
+                  <c:v>4322</c:v>
+                </c:pt>
+                <c:pt idx="96">
+                  <c:v>4407</c:v>
+                </c:pt>
+                <c:pt idx="97">
+                  <c:v>4374</c:v>
+                </c:pt>
+                <c:pt idx="98">
+                  <c:v>4303</c:v>
+                </c:pt>
+                <c:pt idx="99">
+                  <c:v>4263</c:v>
+                </c:pt>
+                <c:pt idx="100">
+                  <c:v>4302</c:v>
+                </c:pt>
+                <c:pt idx="102">
+                  <c:v>4296</c:v>
+                </c:pt>
+                <c:pt idx="103">
+                  <c:v>4336</c:v>
+                </c:pt>
+                <c:pt idx="104">
+                  <c:v>4219</c:v>
+                </c:pt>
+                <c:pt idx="105">
+                  <c:v>3994</c:v>
+                </c:pt>
+                <c:pt idx="106">
+                  <c:v>4022</c:v>
+                </c:pt>
+                <c:pt idx="108">
+                  <c:v>4228</c:v>
+                </c:pt>
+                <c:pt idx="109">
+                  <c:v>4323</c:v>
+                </c:pt>
+                <c:pt idx="110">
+                  <c:v>4261</c:v>
+                </c:pt>
+                <c:pt idx="111">
+                  <c:v>4310</c:v>
+                </c:pt>
+                <c:pt idx="112">
+                  <c:v>4329</c:v>
+                </c:pt>
+                <c:pt idx="114">
+                  <c:v>4447</c:v>
+                </c:pt>
+                <c:pt idx="115">
+                  <c:v>4518</c:v>
+                </c:pt>
+                <c:pt idx="116">
+                  <c:v>4262</c:v>
+                </c:pt>
+                <c:pt idx="117">
+                  <c:v>4352</c:v>
+                </c:pt>
+                <c:pt idx="118">
+                  <c:v>4285</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>Sheet1!$AI$5:$AI$123</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="119"/>
+                <c:pt idx="0">
+                  <c:v>27</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>27</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>30</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>29</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>29</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>30</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>27</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>30</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>28</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>39</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>28</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>27</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>28</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>29</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>28</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>29</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>28</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>29</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>28</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>27</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>30</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>29</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>28</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>27</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>27</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>28</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>29</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>27</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>28</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>27</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>26</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>29</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>27</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>29</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>28</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>28</c:v>
+                </c:pt>
+                <c:pt idx="43">
+                  <c:v>29</c:v>
+                </c:pt>
+                <c:pt idx="44">
+                  <c:v>28</c:v>
+                </c:pt>
+                <c:pt idx="45">
+                  <c:v>29</c:v>
+                </c:pt>
+                <c:pt idx="46">
+                  <c:v>29</c:v>
+                </c:pt>
+                <c:pt idx="48">
+                  <c:v>29</c:v>
+                </c:pt>
+                <c:pt idx="49">
+                  <c:v>30</c:v>
+                </c:pt>
+                <c:pt idx="50">
+                  <c:v>28</c:v>
+                </c:pt>
+                <c:pt idx="51">
+                  <c:v>29</c:v>
+                </c:pt>
+                <c:pt idx="52">
+                  <c:v>29</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>29</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>28</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>27</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>23</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>28</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>30</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>28</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>28</c:v>
+                </c:pt>
+                <c:pt idx="63">
+                  <c:v>29</c:v>
+                </c:pt>
+                <c:pt idx="64">
+                  <c:v>30</c:v>
+                </c:pt>
+                <c:pt idx="66">
+                  <c:v>28</c:v>
+                </c:pt>
+                <c:pt idx="67">
+                  <c:v>30</c:v>
+                </c:pt>
+                <c:pt idx="68">
+                  <c:v>29</c:v>
+                </c:pt>
+                <c:pt idx="69">
+                  <c:v>26</c:v>
+                </c:pt>
+                <c:pt idx="70">
+                  <c:v>28</c:v>
+                </c:pt>
+                <c:pt idx="72">
+                  <c:v>27</c:v>
+                </c:pt>
+                <c:pt idx="73">
+                  <c:v>28</c:v>
+                </c:pt>
+                <c:pt idx="74">
+                  <c:v>29</c:v>
+                </c:pt>
+                <c:pt idx="75">
+                  <c:v>25</c:v>
+                </c:pt>
+                <c:pt idx="76">
+                  <c:v>28</c:v>
+                </c:pt>
+                <c:pt idx="78">
+                  <c:v>28</c:v>
+                </c:pt>
+                <c:pt idx="79">
+                  <c:v>27</c:v>
+                </c:pt>
+                <c:pt idx="80">
+                  <c:v>28</c:v>
+                </c:pt>
+                <c:pt idx="81">
+                  <c:v>30</c:v>
+                </c:pt>
+                <c:pt idx="82">
+                  <c:v>29</c:v>
+                </c:pt>
+                <c:pt idx="84">
+                  <c:v>30</c:v>
+                </c:pt>
+                <c:pt idx="85">
+                  <c:v>30</c:v>
+                </c:pt>
+                <c:pt idx="86">
+                  <c:v>29</c:v>
+                </c:pt>
+                <c:pt idx="87">
+                  <c:v>29</c:v>
+                </c:pt>
+                <c:pt idx="88">
+                  <c:v>29</c:v>
+                </c:pt>
+                <c:pt idx="90">
+                  <c:v>29</c:v>
+                </c:pt>
+                <c:pt idx="91">
+                  <c:v>30</c:v>
+                </c:pt>
+                <c:pt idx="92">
+                  <c:v>26</c:v>
+                </c:pt>
+                <c:pt idx="93">
+                  <c:v>28</c:v>
+                </c:pt>
+                <c:pt idx="94">
+                  <c:v>28</c:v>
+                </c:pt>
+                <c:pt idx="96">
+                  <c:v>27</c:v>
+                </c:pt>
+                <c:pt idx="97">
+                  <c:v>29</c:v>
+                </c:pt>
+                <c:pt idx="98">
+                  <c:v>30</c:v>
+                </c:pt>
+                <c:pt idx="99">
+                  <c:v>27</c:v>
+                </c:pt>
+                <c:pt idx="100">
+                  <c:v>30</c:v>
+                </c:pt>
+                <c:pt idx="102">
+                  <c:v>27</c:v>
+                </c:pt>
+                <c:pt idx="103">
+                  <c:v>28</c:v>
+                </c:pt>
+                <c:pt idx="104">
+                  <c:v>29</c:v>
+                </c:pt>
+                <c:pt idx="105">
+                  <c:v>28</c:v>
+                </c:pt>
+                <c:pt idx="106">
+                  <c:v>27</c:v>
+                </c:pt>
+                <c:pt idx="108">
+                  <c:v>26</c:v>
+                </c:pt>
+                <c:pt idx="109">
+                  <c:v>26</c:v>
+                </c:pt>
+                <c:pt idx="110">
+                  <c:v>28</c:v>
+                </c:pt>
+                <c:pt idx="111">
+                  <c:v>29</c:v>
+                </c:pt>
+                <c:pt idx="112">
+                  <c:v>26</c:v>
+                </c:pt>
+                <c:pt idx="114">
+                  <c:v>30</c:v>
+                </c:pt>
+                <c:pt idx="115">
+                  <c:v>27</c:v>
+                </c:pt>
+                <c:pt idx="116">
+                  <c:v>30</c:v>
+                </c:pt>
+                <c:pt idx="117">
+                  <c:v>29</c:v>
+                </c:pt>
+                <c:pt idx="118">
+                  <c:v>29</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-E9F5-40F9-B568-90B8B171D1AC}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:axId val="1435844576"/>
+        <c:axId val="1435845056"/>
+      </c:scatterChart>
+      <c:valAx>
+        <c:axId val="1435844576"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="en-US"/>
+                  <a:t>Time (CPU ticks)</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1435845056"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:valAx>
+        <c:axId val="1435845056"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="en-US"/>
+                  <a:t>fitness</a:t>
+                </a:r>
+                <a:r>
+                  <a:rPr lang="en-US" baseline="0"/>
+                  <a:t> score</a:t>
+                </a:r>
+                <a:endParaRPr lang="en-US"/>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1435844576"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
 <file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
   <a:schemeClr val="accent1"/>
@@ -7631,6 +9679,86 @@
 </cs:colorStyle>
 </file>
 
+<file path=xl/charts/colors8.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors9.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
 <file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
   <cs:axisTitle>
@@ -10728,6 +12856,1038 @@
 </file>
 
 <file path=xl/charts/style7.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style8.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style9.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
   <cs:axisTitle>
     <cs:lnRef idx="0"/>
@@ -11463,16 +14623,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>29</xdr:col>
-      <xdr:colOff>320636</xdr:colOff>
-      <xdr:row>103</xdr:row>
-      <xdr:rowOff>161024</xdr:rowOff>
+      <xdr:col>27</xdr:col>
+      <xdr:colOff>210883</xdr:colOff>
+      <xdr:row>123</xdr:row>
+      <xdr:rowOff>129666</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>33</xdr:col>
-      <xdr:colOff>1215907</xdr:colOff>
-      <xdr:row>119</xdr:row>
-      <xdr:rowOff>19286</xdr:rowOff>
+      <xdr:col>31</xdr:col>
+      <xdr:colOff>259487</xdr:colOff>
+      <xdr:row>138</xdr:row>
+      <xdr:rowOff>168236</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -11492,6 +14652,78 @@
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
           <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId7"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>30</xdr:col>
+      <xdr:colOff>602859</xdr:colOff>
+      <xdr:row>124</xdr:row>
+      <xdr:rowOff>90467</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>34</xdr:col>
+      <xdr:colOff>643624</xdr:colOff>
+      <xdr:row>139</xdr:row>
+      <xdr:rowOff>129038</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="9" name="Chart 8">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F8D3504D-C342-C53D-3AEF-80B696C6C20B}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId8"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>33</xdr:col>
+      <xdr:colOff>116807</xdr:colOff>
+      <xdr:row>124</xdr:row>
+      <xdr:rowOff>121825</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>38</xdr:col>
+      <xdr:colOff>384918</xdr:colOff>
+      <xdr:row>139</xdr:row>
+      <xdr:rowOff>160396</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="10" name="Chart 9">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9C9B6E97-F473-D81F-F039-7FFC2DA5EDD5}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId9"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -11837,6 +15069,7 @@
     <col min="27" max="27" width="10.453125" customWidth="1"/>
     <col min="28" max="28" width="20.54296875" customWidth="1"/>
     <col min="29" max="29" width="14.453125" customWidth="1"/>
+    <col min="30" max="30" width="15.26953125" customWidth="1"/>
     <col min="31" max="31" width="21" customWidth="1"/>
     <col min="32" max="32" width="14.1796875" customWidth="1"/>
     <col min="34" max="34" width="21" customWidth="1"/>
@@ -11856,6 +15089,8 @@
       <c r="I1" s="1"/>
       <c r="J1" s="1"/>
       <c r="K1" s="1"/>
+      <c r="L1" s="2"/>
+      <c r="M1" s="2"/>
       <c r="N1" s="1" t="s">
         <v>31</v>
       </c>
@@ -11868,6 +15103,8 @@
       <c r="U1" s="1"/>
       <c r="V1" s="1"/>
       <c r="W1" s="1"/>
+      <c r="X1" s="3"/>
+      <c r="Y1" s="3"/>
       <c r="Z1" s="1" t="s">
         <v>32</v>
       </c>
@@ -11894,6 +15131,8 @@
         <v>29</v>
       </c>
       <c r="K2" s="1"/>
+      <c r="L2" s="2"/>
+      <c r="M2" s="2"/>
       <c r="P2" s="1" t="s">
         <v>28</v>
       </c>
@@ -11906,13 +15145,20 @@
         <v>29</v>
       </c>
       <c r="W2" s="1"/>
+      <c r="X2" s="3"/>
+      <c r="Y2" s="3"/>
       <c r="AB2" s="1" t="s">
         <v>28</v>
       </c>
       <c r="AC2" s="1"/>
-      <c r="AE2" s="1"/>
+      <c r="AD2" s="4"/>
+      <c r="AE2" s="1" t="s">
+        <v>27</v>
+      </c>
       <c r="AF2" s="1"/>
-      <c r="AH2" s="1"/>
+      <c r="AH2" s="1" t="s">
+        <v>29</v>
+      </c>
       <c r="AI2" s="1"/>
     </row>
     <row r="3" spans="2:35" x14ac:dyDescent="0.35">
@@ -11934,6 +15180,8 @@
       <c r="K3" t="s">
         <v>26</v>
       </c>
+      <c r="L3" s="2"/>
+      <c r="M3" s="2"/>
       <c r="P3" t="s">
         <v>25</v>
       </c>
@@ -11952,10 +15200,24 @@
       <c r="W3" t="s">
         <v>26</v>
       </c>
+      <c r="X3" s="3"/>
+      <c r="Y3" s="3"/>
       <c r="AB3" t="s">
         <v>25</v>
       </c>
       <c r="AC3" t="s">
+        <v>26</v>
+      </c>
+      <c r="AE3" t="s">
+        <v>25</v>
+      </c>
+      <c r="AF3" t="s">
+        <v>26</v>
+      </c>
+      <c r="AH3" t="s">
+        <v>25</v>
+      </c>
+      <c r="AI3" t="s">
         <v>26</v>
       </c>
     </row>
@@ -11963,9 +15225,13 @@
       <c r="B4" t="s">
         <v>0</v>
       </c>
+      <c r="L4" s="2"/>
+      <c r="M4" s="2"/>
       <c r="N4" t="s">
         <v>0</v>
       </c>
+      <c r="X4" s="3"/>
+      <c r="Y4" s="3"/>
       <c r="Z4" t="s">
         <v>0</v>
       </c>
@@ -11992,6 +15258,8 @@
       <c r="K5">
         <v>16</v>
       </c>
+      <c r="L5" s="2"/>
+      <c r="M5" s="2"/>
       <c r="O5" t="s">
         <v>1</v>
       </c>
@@ -12013,6 +15281,8 @@
       <c r="W5">
         <v>6</v>
       </c>
+      <c r="X5" s="3"/>
+      <c r="Y5" s="3"/>
       <c r="AA5" t="s">
         <v>1</v>
       </c>
@@ -12020,6 +15290,18 @@
         <v>4062</v>
       </c>
       <c r="AC5">
+        <v>27</v>
+      </c>
+      <c r="AE5">
+        <v>4049</v>
+      </c>
+      <c r="AF5">
+        <v>28</v>
+      </c>
+      <c r="AH5">
+        <v>3810</v>
+      </c>
+      <c r="AI5">
         <v>27</v>
       </c>
     </row>
@@ -12045,6 +15327,8 @@
       <c r="K6">
         <v>18</v>
       </c>
+      <c r="L6" s="2"/>
+      <c r="M6" s="2"/>
       <c r="O6" t="s">
         <v>2</v>
       </c>
@@ -12066,6 +15350,8 @@
       <c r="W6">
         <v>12</v>
       </c>
+      <c r="X6" s="3"/>
+      <c r="Y6" s="3"/>
       <c r="AA6" t="s">
         <v>2</v>
       </c>
@@ -12074,6 +15360,18 @@
       </c>
       <c r="AC6">
         <v>29</v>
+      </c>
+      <c r="AE6">
+        <v>4072</v>
+      </c>
+      <c r="AF6">
+        <v>30</v>
+      </c>
+      <c r="AH6">
+        <v>3765</v>
+      </c>
+      <c r="AI6">
+        <v>27</v>
       </c>
     </row>
     <row r="7" spans="2:35" x14ac:dyDescent="0.35">
@@ -12098,6 +15396,8 @@
       <c r="K7">
         <v>16</v>
       </c>
+      <c r="L7" s="2"/>
+      <c r="M7" s="2"/>
       <c r="O7" t="s">
         <v>3</v>
       </c>
@@ -12119,6 +15419,8 @@
       <c r="W7">
         <v>7</v>
       </c>
+      <c r="X7" s="3"/>
+      <c r="Y7" s="3"/>
       <c r="AA7" t="s">
         <v>3</v>
       </c>
@@ -12127,6 +15429,18 @@
       </c>
       <c r="AC7">
         <v>31</v>
+      </c>
+      <c r="AE7">
+        <v>4053</v>
+      </c>
+      <c r="AF7">
+        <v>28</v>
+      </c>
+      <c r="AH7">
+        <v>3758</v>
+      </c>
+      <c r="AI7">
+        <v>30</v>
       </c>
     </row>
     <row r="8" spans="2:35" x14ac:dyDescent="0.35">
@@ -12151,6 +15465,8 @@
       <c r="K8">
         <v>20</v>
       </c>
+      <c r="L8" s="2"/>
+      <c r="M8" s="2"/>
       <c r="O8" t="s">
         <v>4</v>
       </c>
@@ -12172,6 +15488,8 @@
       <c r="W8">
         <v>13</v>
       </c>
+      <c r="X8" s="3"/>
+      <c r="Y8" s="3"/>
       <c r="AA8" t="s">
         <v>4</v>
       </c>
@@ -12180,6 +15498,18 @@
       </c>
       <c r="AC8">
         <v>28</v>
+      </c>
+      <c r="AE8">
+        <v>4088</v>
+      </c>
+      <c r="AF8">
+        <v>29</v>
+      </c>
+      <c r="AH8">
+        <v>3846</v>
+      </c>
+      <c r="AI8">
+        <v>29</v>
       </c>
     </row>
     <row r="9" spans="2:35" x14ac:dyDescent="0.35">
@@ -12204,6 +15534,8 @@
       <c r="K9">
         <v>18</v>
       </c>
+      <c r="L9" s="2"/>
+      <c r="M9" s="2"/>
       <c r="O9" t="s">
         <v>5</v>
       </c>
@@ -12225,6 +15557,8 @@
       <c r="W9">
         <v>12</v>
       </c>
+      <c r="X9" s="3"/>
+      <c r="Y9" s="3"/>
       <c r="AA9" t="s">
         <v>5</v>
       </c>
@@ -12233,15 +15567,31 @@
       </c>
       <c r="AC9">
         <v>28</v>
+      </c>
+      <c r="AE9">
+        <v>4056</v>
+      </c>
+      <c r="AF9">
+        <v>28</v>
+      </c>
+      <c r="AH9">
+        <v>3852</v>
+      </c>
+      <c r="AI9">
+        <v>29</v>
       </c>
     </row>
     <row r="10" spans="2:35" x14ac:dyDescent="0.35">
       <c r="B10" t="s">
         <v>6</v>
       </c>
+      <c r="L10" s="2"/>
+      <c r="M10" s="2"/>
       <c r="N10" t="s">
         <v>6</v>
       </c>
+      <c r="X10" s="3"/>
+      <c r="Y10" s="3"/>
       <c r="Z10" t="s">
         <v>6</v>
       </c>
@@ -12268,6 +15618,8 @@
       <c r="K11">
         <v>15</v>
       </c>
+      <c r="L11" s="2"/>
+      <c r="M11" s="2"/>
       <c r="O11" t="s">
         <v>1</v>
       </c>
@@ -12289,6 +15641,8 @@
       <c r="W11">
         <v>10</v>
       </c>
+      <c r="X11" s="3"/>
+      <c r="Y11" s="3"/>
       <c r="AA11" t="s">
         <v>1</v>
       </c>
@@ -12297,6 +15651,18 @@
       </c>
       <c r="AC11">
         <v>29</v>
+      </c>
+      <c r="AE11">
+        <v>4036</v>
+      </c>
+      <c r="AF11">
+        <v>28</v>
+      </c>
+      <c r="AH11">
+        <v>3779</v>
+      </c>
+      <c r="AI11">
+        <v>30</v>
       </c>
     </row>
     <row r="12" spans="2:35" x14ac:dyDescent="0.35">
@@ -12321,6 +15687,8 @@
       <c r="K12">
         <v>16</v>
       </c>
+      <c r="L12" s="2"/>
+      <c r="M12" s="2"/>
       <c r="O12" t="s">
         <v>2</v>
       </c>
@@ -12342,6 +15710,8 @@
       <c r="W12">
         <v>11</v>
       </c>
+      <c r="X12" s="3"/>
+      <c r="Y12" s="3"/>
       <c r="AA12" t="s">
         <v>2</v>
       </c>
@@ -12349,6 +15719,18 @@
         <v>4212</v>
       </c>
       <c r="AC12">
+        <v>27</v>
+      </c>
+      <c r="AE12">
+        <v>4009</v>
+      </c>
+      <c r="AF12">
+        <v>27</v>
+      </c>
+      <c r="AH12">
+        <v>3766</v>
+      </c>
+      <c r="AI12">
         <v>27</v>
       </c>
     </row>
@@ -12374,6 +15756,8 @@
       <c r="K13">
         <v>14</v>
       </c>
+      <c r="L13" s="2"/>
+      <c r="M13" s="2"/>
       <c r="O13" t="s">
         <v>3</v>
       </c>
@@ -12395,6 +15779,8 @@
       <c r="W13">
         <v>4</v>
       </c>
+      <c r="X13" s="3"/>
+      <c r="Y13" s="3"/>
       <c r="AA13" t="s">
         <v>3</v>
       </c>
@@ -12403,6 +15789,18 @@
       </c>
       <c r="AC13">
         <v>28</v>
+      </c>
+      <c r="AE13">
+        <v>4055</v>
+      </c>
+      <c r="AF13">
+        <v>28</v>
+      </c>
+      <c r="AH13">
+        <v>3813</v>
+      </c>
+      <c r="AI13">
+        <v>30</v>
       </c>
     </row>
     <row r="14" spans="2:35" x14ac:dyDescent="0.35">
@@ -12427,6 +15825,8 @@
       <c r="K14">
         <v>12</v>
       </c>
+      <c r="L14" s="2"/>
+      <c r="M14" s="2"/>
       <c r="O14" t="s">
         <v>4</v>
       </c>
@@ -12448,6 +15848,8 @@
       <c r="W14">
         <v>11</v>
       </c>
+      <c r="X14" s="3"/>
+      <c r="Y14" s="3"/>
       <c r="AA14" t="s">
         <v>4</v>
       </c>
@@ -12455,6 +15857,18 @@
         <v>4270</v>
       </c>
       <c r="AC14">
+        <v>28</v>
+      </c>
+      <c r="AE14">
+        <v>4093</v>
+      </c>
+      <c r="AF14">
+        <v>30</v>
+      </c>
+      <c r="AH14">
+        <v>3935</v>
+      </c>
+      <c r="AI14">
         <v>28</v>
       </c>
     </row>
@@ -12480,6 +15894,8 @@
       <c r="K15">
         <v>18</v>
       </c>
+      <c r="L15" s="2"/>
+      <c r="M15" s="2"/>
       <c r="O15" t="s">
         <v>5</v>
       </c>
@@ -12501,6 +15917,8 @@
       <c r="W15">
         <v>11</v>
       </c>
+      <c r="X15" s="3"/>
+      <c r="Y15" s="3"/>
       <c r="AA15" t="s">
         <v>5</v>
       </c>
@@ -12509,20 +15927,36 @@
       </c>
       <c r="AC15">
         <v>26</v>
+      </c>
+      <c r="AE15">
+        <v>4031</v>
+      </c>
+      <c r="AF15">
+        <v>28</v>
+      </c>
+      <c r="AH15">
+        <v>3752</v>
+      </c>
+      <c r="AI15">
+        <v>39</v>
       </c>
     </row>
     <row r="16" spans="2:35" x14ac:dyDescent="0.35">
       <c r="B16" t="s">
         <v>8</v>
       </c>
+      <c r="L16" s="2"/>
+      <c r="M16" s="2"/>
       <c r="N16" t="s">
         <v>8</v>
       </c>
+      <c r="X16" s="3"/>
+      <c r="Y16" s="3"/>
       <c r="Z16" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="17" spans="2:29" x14ac:dyDescent="0.35">
+    <row r="17" spans="2:35" x14ac:dyDescent="0.35">
       <c r="C17" t="s">
         <v>1</v>
       </c>
@@ -12544,6 +15978,8 @@
       <c r="K17">
         <v>19</v>
       </c>
+      <c r="L17" s="2"/>
+      <c r="M17" s="2"/>
       <c r="O17" t="s">
         <v>1</v>
       </c>
@@ -12565,6 +16001,8 @@
       <c r="W17">
         <v>6</v>
       </c>
+      <c r="X17" s="3"/>
+      <c r="Y17" s="3"/>
       <c r="AA17" t="s">
         <v>1</v>
       </c>
@@ -12574,8 +16012,20 @@
       <c r="AC17">
         <v>28</v>
       </c>
+      <c r="AE17">
+        <v>4101</v>
+      </c>
+      <c r="AF17">
+        <v>29</v>
+      </c>
+      <c r="AH17">
+        <v>3738</v>
+      </c>
+      <c r="AI17">
+        <v>28</v>
+      </c>
     </row>
-    <row r="18" spans="2:29" x14ac:dyDescent="0.35">
+    <row r="18" spans="2:35" x14ac:dyDescent="0.35">
       <c r="C18" t="s">
         <v>2</v>
       </c>
@@ -12597,6 +16047,8 @@
       <c r="K18">
         <v>19</v>
       </c>
+      <c r="L18" s="2"/>
+      <c r="M18" s="2"/>
       <c r="O18" t="s">
         <v>2</v>
       </c>
@@ -12618,6 +16070,8 @@
       <c r="W18">
         <v>6</v>
       </c>
+      <c r="X18" s="3"/>
+      <c r="Y18" s="3"/>
       <c r="AA18" t="s">
         <v>2</v>
       </c>
@@ -12627,8 +16081,20 @@
       <c r="AC18">
         <v>28</v>
       </c>
+      <c r="AE18">
+        <v>4069</v>
+      </c>
+      <c r="AF18">
+        <v>28</v>
+      </c>
+      <c r="AH18">
+        <v>3731</v>
+      </c>
+      <c r="AI18">
+        <v>27</v>
+      </c>
     </row>
-    <row r="19" spans="2:29" x14ac:dyDescent="0.35">
+    <row r="19" spans="2:35" x14ac:dyDescent="0.35">
       <c r="C19" t="s">
         <v>3</v>
       </c>
@@ -12650,6 +16116,8 @@
       <c r="K19">
         <v>21</v>
       </c>
+      <c r="L19" s="2"/>
+      <c r="M19" s="2"/>
       <c r="O19" t="s">
         <v>3</v>
       </c>
@@ -12671,6 +16139,8 @@
       <c r="W19">
         <v>9</v>
       </c>
+      <c r="X19" s="3"/>
+      <c r="Y19" s="3"/>
       <c r="AA19" t="s">
         <v>3</v>
       </c>
@@ -12680,8 +16150,20 @@
       <c r="AC19">
         <v>30</v>
       </c>
+      <c r="AE19">
+        <v>4091</v>
+      </c>
+      <c r="AF19">
+        <v>27</v>
+      </c>
+      <c r="AH19">
+        <v>3716</v>
+      </c>
+      <c r="AI19">
+        <v>28</v>
+      </c>
     </row>
-    <row r="20" spans="2:29" x14ac:dyDescent="0.35">
+    <row r="20" spans="2:35" x14ac:dyDescent="0.35">
       <c r="C20" t="s">
         <v>4</v>
       </c>
@@ -12703,6 +16185,8 @@
       <c r="K20">
         <v>21</v>
       </c>
+      <c r="L20" s="2"/>
+      <c r="M20" s="2"/>
       <c r="O20" t="s">
         <v>4</v>
       </c>
@@ -12724,6 +16208,8 @@
       <c r="W20">
         <v>8</v>
       </c>
+      <c r="X20" s="3"/>
+      <c r="Y20" s="3"/>
       <c r="AA20" t="s">
         <v>4</v>
       </c>
@@ -12733,8 +16219,20 @@
       <c r="AC20">
         <v>27</v>
       </c>
+      <c r="AE20">
+        <v>4051</v>
+      </c>
+      <c r="AF20">
+        <v>29</v>
+      </c>
+      <c r="AH20">
+        <v>3735</v>
+      </c>
+      <c r="AI20">
+        <v>29</v>
+      </c>
     </row>
-    <row r="21" spans="2:29" x14ac:dyDescent="0.35">
+    <row r="21" spans="2:35" x14ac:dyDescent="0.35">
       <c r="C21" t="s">
         <v>5</v>
       </c>
@@ -12756,6 +16254,8 @@
       <c r="K21">
         <v>19</v>
       </c>
+      <c r="L21" s="2"/>
+      <c r="M21" s="2"/>
       <c r="O21" t="s">
         <v>5</v>
       </c>
@@ -12777,6 +16277,8 @@
       <c r="W21">
         <v>7</v>
       </c>
+      <c r="X21" s="3"/>
+      <c r="Y21" s="3"/>
       <c r="AA21" t="s">
         <v>5</v>
       </c>
@@ -12786,19 +16288,35 @@
       <c r="AC21">
         <v>28</v>
       </c>
+      <c r="AE21">
+        <v>4075</v>
+      </c>
+      <c r="AF21">
+        <v>27</v>
+      </c>
+      <c r="AH21">
+        <v>3714</v>
+      </c>
+      <c r="AI21">
+        <v>28</v>
+      </c>
     </row>
-    <row r="22" spans="2:29" x14ac:dyDescent="0.35">
+    <row r="22" spans="2:35" x14ac:dyDescent="0.35">
       <c r="B22" t="s">
         <v>7</v>
       </c>
+      <c r="L22" s="2"/>
+      <c r="M22" s="2"/>
       <c r="N22" t="s">
         <v>7</v>
       </c>
+      <c r="X22" s="3"/>
+      <c r="Y22" s="3"/>
       <c r="Z22" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="23" spans="2:29" x14ac:dyDescent="0.35">
+    <row r="23" spans="2:35" x14ac:dyDescent="0.35">
       <c r="C23" t="s">
         <v>1</v>
       </c>
@@ -12820,6 +16338,8 @@
       <c r="K23">
         <v>12</v>
       </c>
+      <c r="L23" s="2"/>
+      <c r="M23" s="2"/>
       <c r="O23" t="s">
         <v>1</v>
       </c>
@@ -12841,6 +16361,8 @@
       <c r="W23">
         <v>12</v>
       </c>
+      <c r="X23" s="3"/>
+      <c r="Y23" s="3"/>
       <c r="AA23" t="s">
         <v>1</v>
       </c>
@@ -12850,8 +16372,20 @@
       <c r="AC23">
         <v>28</v>
       </c>
+      <c r="AE23">
+        <v>3982</v>
+      </c>
+      <c r="AF23">
+        <v>27</v>
+      </c>
+      <c r="AH23">
+        <v>3737</v>
+      </c>
+      <c r="AI23">
+        <v>29</v>
+      </c>
     </row>
-    <row r="24" spans="2:29" x14ac:dyDescent="0.35">
+    <row r="24" spans="2:35" x14ac:dyDescent="0.35">
       <c r="C24" t="s">
         <v>2</v>
       </c>
@@ -12873,6 +16407,8 @@
       <c r="K24">
         <v>17</v>
       </c>
+      <c r="L24" s="2"/>
+      <c r="M24" s="2"/>
       <c r="O24" t="s">
         <v>2</v>
       </c>
@@ -12894,6 +16430,8 @@
       <c r="W24">
         <v>10</v>
       </c>
+      <c r="X24" s="3"/>
+      <c r="Y24" s="3"/>
       <c r="AA24" t="s">
         <v>2</v>
       </c>
@@ -12903,8 +16441,20 @@
       <c r="AC24">
         <v>29</v>
       </c>
+      <c r="AE24">
+        <v>3973</v>
+      </c>
+      <c r="AF24">
+        <v>28</v>
+      </c>
+      <c r="AH24">
+        <v>3762</v>
+      </c>
+      <c r="AI24">
+        <v>28</v>
+      </c>
     </row>
-    <row r="25" spans="2:29" x14ac:dyDescent="0.35">
+    <row r="25" spans="2:35" x14ac:dyDescent="0.35">
       <c r="C25" t="s">
         <v>3</v>
       </c>
@@ -12926,6 +16476,8 @@
       <c r="K25">
         <v>18</v>
       </c>
+      <c r="L25" s="2"/>
+      <c r="M25" s="2"/>
       <c r="O25" t="s">
         <v>3</v>
       </c>
@@ -12947,6 +16499,8 @@
       <c r="W25">
         <v>11</v>
       </c>
+      <c r="X25" s="3"/>
+      <c r="Y25" s="3"/>
       <c r="AA25" t="s">
         <v>3</v>
       </c>
@@ -12956,8 +16510,20 @@
       <c r="AC25">
         <v>28</v>
       </c>
+      <c r="AE25">
+        <v>3962</v>
+      </c>
+      <c r="AF25">
+        <v>30</v>
+      </c>
+      <c r="AH25">
+        <v>3714</v>
+      </c>
+      <c r="AI25">
+        <v>29</v>
+      </c>
     </row>
-    <row r="26" spans="2:29" x14ac:dyDescent="0.35">
+    <row r="26" spans="2:35" x14ac:dyDescent="0.35">
       <c r="C26" t="s">
         <v>4</v>
       </c>
@@ -12979,6 +16545,8 @@
       <c r="K26">
         <v>17</v>
       </c>
+      <c r="L26" s="2"/>
+      <c r="M26" s="2"/>
       <c r="O26" t="s">
         <v>4</v>
       </c>
@@ -13000,6 +16568,8 @@
       <c r="W26">
         <v>4</v>
       </c>
+      <c r="X26" s="3"/>
+      <c r="Y26" s="3"/>
       <c r="AA26" t="s">
         <v>4</v>
       </c>
@@ -13009,8 +16579,20 @@
       <c r="AC26">
         <v>28</v>
       </c>
+      <c r="AE26">
+        <v>3958</v>
+      </c>
+      <c r="AF26">
+        <v>30</v>
+      </c>
+      <c r="AH26">
+        <v>3700</v>
+      </c>
+      <c r="AI26">
+        <v>28</v>
+      </c>
     </row>
-    <row r="27" spans="2:29" x14ac:dyDescent="0.35">
+    <row r="27" spans="2:35" x14ac:dyDescent="0.35">
       <c r="C27" t="s">
         <v>5</v>
       </c>
@@ -13032,6 +16614,8 @@
       <c r="K27">
         <v>20</v>
       </c>
+      <c r="L27" s="2"/>
+      <c r="M27" s="2"/>
       <c r="O27" t="s">
         <v>5</v>
       </c>
@@ -13053,6 +16637,8 @@
       <c r="W27">
         <v>8</v>
       </c>
+      <c r="X27" s="3"/>
+      <c r="Y27" s="3"/>
       <c r="AA27" t="s">
         <v>5</v>
       </c>
@@ -13062,19 +16648,35 @@
       <c r="AC27">
         <v>29</v>
       </c>
+      <c r="AE27">
+        <v>3973</v>
+      </c>
+      <c r="AF27">
+        <v>27</v>
+      </c>
+      <c r="AH27">
+        <v>3720</v>
+      </c>
+      <c r="AI27">
+        <v>27</v>
+      </c>
     </row>
-    <row r="28" spans="2:29" x14ac:dyDescent="0.35">
+    <row r="28" spans="2:35" x14ac:dyDescent="0.35">
       <c r="B28" t="s">
         <v>9</v>
       </c>
+      <c r="L28" s="2"/>
+      <c r="M28" s="2"/>
       <c r="N28" t="s">
         <v>9</v>
       </c>
+      <c r="X28" s="3"/>
+      <c r="Y28" s="3"/>
       <c r="Z28" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="29" spans="2:29" x14ac:dyDescent="0.35">
+    <row r="29" spans="2:35" x14ac:dyDescent="0.35">
       <c r="C29" t="s">
         <v>1</v>
       </c>
@@ -13096,6 +16698,8 @@
       <c r="K29">
         <v>20</v>
       </c>
+      <c r="L29" s="2"/>
+      <c r="M29" s="2"/>
       <c r="O29" t="s">
         <v>1</v>
       </c>
@@ -13117,6 +16721,8 @@
       <c r="W29">
         <v>9</v>
       </c>
+      <c r="X29" s="3"/>
+      <c r="Y29" s="3"/>
       <c r="AA29" t="s">
         <v>1</v>
       </c>
@@ -13126,8 +16732,20 @@
       <c r="AC29">
         <v>28</v>
       </c>
+      <c r="AE29">
+        <v>4053</v>
+      </c>
+      <c r="AF29">
+        <v>29</v>
+      </c>
+      <c r="AH29">
+        <v>3738</v>
+      </c>
+      <c r="AI29">
+        <v>30</v>
+      </c>
     </row>
-    <row r="30" spans="2:29" x14ac:dyDescent="0.35">
+    <row r="30" spans="2:35" x14ac:dyDescent="0.35">
       <c r="C30" t="s">
         <v>2</v>
       </c>
@@ -13149,6 +16767,8 @@
       <c r="K30">
         <v>20</v>
       </c>
+      <c r="L30" s="2"/>
+      <c r="M30" s="2"/>
       <c r="O30" t="s">
         <v>2</v>
       </c>
@@ -13170,6 +16790,8 @@
       <c r="W30">
         <v>8</v>
       </c>
+      <c r="X30" s="3"/>
+      <c r="Y30" s="3"/>
       <c r="AA30" t="s">
         <v>2</v>
       </c>
@@ -13179,8 +16801,20 @@
       <c r="AC30">
         <v>27</v>
       </c>
+      <c r="AE30">
+        <v>4090</v>
+      </c>
+      <c r="AF30">
+        <v>30</v>
+      </c>
+      <c r="AH30">
+        <v>3709</v>
+      </c>
+      <c r="AI30">
+        <v>29</v>
+      </c>
     </row>
-    <row r="31" spans="2:29" x14ac:dyDescent="0.35">
+    <row r="31" spans="2:35" x14ac:dyDescent="0.35">
       <c r="C31" t="s">
         <v>3</v>
       </c>
@@ -13202,6 +16836,8 @@
       <c r="K31">
         <v>20</v>
       </c>
+      <c r="L31" s="2"/>
+      <c r="M31" s="2"/>
       <c r="O31" t="s">
         <v>3</v>
       </c>
@@ -13223,6 +16859,8 @@
       <c r="W31">
         <v>8</v>
       </c>
+      <c r="X31" s="3"/>
+      <c r="Y31" s="3"/>
       <c r="AA31" t="s">
         <v>3</v>
       </c>
@@ -13232,8 +16870,20 @@
       <c r="AC31">
         <v>30</v>
       </c>
+      <c r="AE31">
+        <v>4078</v>
+      </c>
+      <c r="AF31">
+        <v>30</v>
+      </c>
+      <c r="AH31">
+        <v>3692</v>
+      </c>
+      <c r="AI31">
+        <v>28</v>
+      </c>
     </row>
-    <row r="32" spans="2:29" x14ac:dyDescent="0.35">
+    <row r="32" spans="2:35" x14ac:dyDescent="0.35">
       <c r="C32" t="s">
         <v>4</v>
       </c>
@@ -13255,6 +16905,8 @@
       <c r="K32">
         <v>22</v>
       </c>
+      <c r="L32" s="2"/>
+      <c r="M32" s="2"/>
       <c r="O32" t="s">
         <v>4</v>
       </c>
@@ -13276,6 +16928,8 @@
       <c r="W32">
         <v>8</v>
       </c>
+      <c r="X32" s="3"/>
+      <c r="Y32" s="3"/>
       <c r="AA32" t="s">
         <v>4</v>
       </c>
@@ -13285,8 +16939,20 @@
       <c r="AC32">
         <v>29</v>
       </c>
+      <c r="AE32">
+        <v>4052</v>
+      </c>
+      <c r="AF32">
+        <v>28</v>
+      </c>
+      <c r="AH32">
+        <v>3757</v>
+      </c>
+      <c r="AI32">
+        <v>27</v>
+      </c>
     </row>
-    <row r="33" spans="2:29" x14ac:dyDescent="0.35">
+    <row r="33" spans="2:35" x14ac:dyDescent="0.35">
       <c r="C33" t="s">
         <v>5</v>
       </c>
@@ -13308,6 +16974,8 @@
       <c r="K33">
         <v>19</v>
       </c>
+      <c r="L33" s="2"/>
+      <c r="M33" s="2"/>
       <c r="O33" t="s">
         <v>5</v>
       </c>
@@ -13329,6 +16997,8 @@
       <c r="W33">
         <v>5</v>
       </c>
+      <c r="X33" s="3"/>
+      <c r="Y33" s="3"/>
       <c r="AA33" t="s">
         <v>5</v>
       </c>
@@ -13338,19 +17008,35 @@
       <c r="AC33">
         <v>26</v>
       </c>
+      <c r="AE33">
+        <v>4044</v>
+      </c>
+      <c r="AF33">
+        <v>28</v>
+      </c>
+      <c r="AH33">
+        <v>3716</v>
+      </c>
+      <c r="AI33">
+        <v>27</v>
+      </c>
     </row>
-    <row r="34" spans="2:29" x14ac:dyDescent="0.35">
+    <row r="34" spans="2:35" x14ac:dyDescent="0.35">
       <c r="B34" t="s">
         <v>10</v>
       </c>
+      <c r="L34" s="2"/>
+      <c r="M34" s="2"/>
       <c r="N34" t="s">
         <v>10</v>
       </c>
+      <c r="X34" s="3"/>
+      <c r="Y34" s="3"/>
       <c r="Z34" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="35" spans="2:29" x14ac:dyDescent="0.35">
+    <row r="35" spans="2:35" x14ac:dyDescent="0.35">
       <c r="C35" t="s">
         <v>1</v>
       </c>
@@ -13372,6 +17058,8 @@
       <c r="K35">
         <v>19</v>
       </c>
+      <c r="L35" s="2"/>
+      <c r="M35" s="2"/>
       <c r="O35" t="s">
         <v>1</v>
       </c>
@@ -13393,6 +17081,8 @@
       <c r="W35">
         <v>9</v>
       </c>
+      <c r="X35" s="3"/>
+      <c r="Y35" s="3"/>
       <c r="AA35" t="s">
         <v>1</v>
       </c>
@@ -13402,8 +17092,20 @@
       <c r="AC35">
         <v>29</v>
       </c>
+      <c r="AE35">
+        <v>3956</v>
+      </c>
+      <c r="AF35">
+        <v>28</v>
+      </c>
+      <c r="AH35">
+        <v>3724</v>
+      </c>
+      <c r="AI35">
+        <v>28</v>
+      </c>
     </row>
-    <row r="36" spans="2:29" x14ac:dyDescent="0.35">
+    <row r="36" spans="2:35" x14ac:dyDescent="0.35">
       <c r="C36" t="s">
         <v>2</v>
       </c>
@@ -13425,6 +17127,8 @@
       <c r="K36">
         <v>16</v>
       </c>
+      <c r="L36" s="2"/>
+      <c r="M36" s="2"/>
       <c r="O36" t="s">
         <v>2</v>
       </c>
@@ -13446,6 +17150,8 @@
       <c r="W36">
         <v>8</v>
       </c>
+      <c r="X36" s="3"/>
+      <c r="Y36" s="3"/>
       <c r="AA36" t="s">
         <v>2</v>
       </c>
@@ -13455,8 +17161,20 @@
       <c r="AC36">
         <v>21</v>
       </c>
+      <c r="AE36">
+        <v>4306</v>
+      </c>
+      <c r="AF36">
+        <v>28</v>
+      </c>
+      <c r="AH36">
+        <v>3718</v>
+      </c>
+      <c r="AI36">
+        <v>29</v>
+      </c>
     </row>
-    <row r="37" spans="2:29" x14ac:dyDescent="0.35">
+    <row r="37" spans="2:35" x14ac:dyDescent="0.35">
       <c r="C37" t="s">
         <v>3</v>
       </c>
@@ -13478,6 +17196,8 @@
       <c r="K37">
         <v>13</v>
       </c>
+      <c r="L37" s="2"/>
+      <c r="M37" s="2"/>
       <c r="O37" t="s">
         <v>3</v>
       </c>
@@ -13499,6 +17219,8 @@
       <c r="W37">
         <v>13</v>
       </c>
+      <c r="X37" s="3"/>
+      <c r="Y37" s="3"/>
       <c r="AA37" t="s">
         <v>3</v>
       </c>
@@ -13508,8 +17230,20 @@
       <c r="AC37">
         <v>28</v>
       </c>
+      <c r="AE37">
+        <v>4134</v>
+      </c>
+      <c r="AF37">
+        <v>29</v>
+      </c>
+      <c r="AH37">
+        <v>3735</v>
+      </c>
+      <c r="AI37">
+        <v>27</v>
+      </c>
     </row>
-    <row r="38" spans="2:29" x14ac:dyDescent="0.35">
+    <row r="38" spans="2:35" x14ac:dyDescent="0.35">
       <c r="C38" t="s">
         <v>4</v>
       </c>
@@ -13531,6 +17265,8 @@
       <c r="K38">
         <v>17</v>
       </c>
+      <c r="L38" s="2"/>
+      <c r="M38" s="2"/>
       <c r="O38" t="s">
         <v>4</v>
       </c>
@@ -13552,6 +17288,8 @@
       <c r="W38">
         <v>4</v>
       </c>
+      <c r="X38" s="3"/>
+      <c r="Y38" s="3"/>
       <c r="AA38" t="s">
         <v>4</v>
       </c>
@@ -13561,8 +17299,20 @@
       <c r="AC38">
         <v>29</v>
       </c>
+      <c r="AE38">
+        <v>4614</v>
+      </c>
+      <c r="AF38">
+        <v>28</v>
+      </c>
+      <c r="AH38">
+        <v>3774</v>
+      </c>
+      <c r="AI38">
+        <v>28</v>
+      </c>
     </row>
-    <row r="39" spans="2:29" x14ac:dyDescent="0.35">
+    <row r="39" spans="2:35" x14ac:dyDescent="0.35">
       <c r="C39" t="s">
         <v>5</v>
       </c>
@@ -13584,6 +17334,8 @@
       <c r="K39">
         <v>18</v>
       </c>
+      <c r="L39" s="2"/>
+      <c r="M39" s="2"/>
       <c r="O39" t="s">
         <v>5</v>
       </c>
@@ -13605,6 +17357,8 @@
       <c r="W39">
         <v>7</v>
       </c>
+      <c r="X39" s="3"/>
+      <c r="Y39" s="3"/>
       <c r="AA39" t="s">
         <v>5</v>
       </c>
@@ -13614,19 +17368,35 @@
       <c r="AC39">
         <v>30</v>
       </c>
+      <c r="AE39">
+        <v>4276</v>
+      </c>
+      <c r="AF39">
+        <v>29</v>
+      </c>
+      <c r="AH39">
+        <v>3773</v>
+      </c>
+      <c r="AI39">
+        <v>27</v>
+      </c>
     </row>
-    <row r="40" spans="2:29" x14ac:dyDescent="0.35">
+    <row r="40" spans="2:35" x14ac:dyDescent="0.35">
       <c r="B40" t="s">
         <v>11</v>
       </c>
+      <c r="L40" s="2"/>
+      <c r="M40" s="2"/>
       <c r="N40" t="s">
         <v>11</v>
       </c>
+      <c r="X40" s="3"/>
+      <c r="Y40" s="3"/>
       <c r="Z40" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="41" spans="2:29" x14ac:dyDescent="0.35">
+    <row r="41" spans="2:35" x14ac:dyDescent="0.35">
       <c r="C41" t="s">
         <v>1</v>
       </c>
@@ -13648,6 +17418,8 @@
       <c r="K41">
         <v>18</v>
       </c>
+      <c r="L41" s="2"/>
+      <c r="M41" s="2"/>
       <c r="O41" t="s">
         <v>1</v>
       </c>
@@ -13669,6 +17441,8 @@
       <c r="W41">
         <v>9</v>
       </c>
+      <c r="X41" s="3"/>
+      <c r="Y41" s="3"/>
       <c r="AA41" t="s">
         <v>1</v>
       </c>
@@ -13678,8 +17452,20 @@
       <c r="AC41">
         <v>29</v>
       </c>
+      <c r="AE41">
+        <v>4478</v>
+      </c>
+      <c r="AF41">
+        <v>28</v>
+      </c>
+      <c r="AH41">
+        <v>3792</v>
+      </c>
+      <c r="AI41">
+        <v>26</v>
+      </c>
     </row>
-    <row r="42" spans="2:29" x14ac:dyDescent="0.35">
+    <row r="42" spans="2:35" x14ac:dyDescent="0.35">
       <c r="C42" t="s">
         <v>2</v>
       </c>
@@ -13701,6 +17487,8 @@
       <c r="K42">
         <v>14</v>
       </c>
+      <c r="L42" s="2"/>
+      <c r="M42" s="2"/>
       <c r="O42" t="s">
         <v>2</v>
       </c>
@@ -13722,6 +17510,8 @@
       <c r="W42">
         <v>10</v>
       </c>
+      <c r="X42" s="3"/>
+      <c r="Y42" s="3"/>
       <c r="AA42" t="s">
         <v>2</v>
       </c>
@@ -13731,8 +17521,20 @@
       <c r="AC42">
         <v>27</v>
       </c>
+      <c r="AE42">
+        <v>4116</v>
+      </c>
+      <c r="AF42">
+        <v>27</v>
+      </c>
+      <c r="AH42">
+        <v>3761</v>
+      </c>
+      <c r="AI42">
+        <v>29</v>
+      </c>
     </row>
-    <row r="43" spans="2:29" x14ac:dyDescent="0.35">
+    <row r="43" spans="2:35" x14ac:dyDescent="0.35">
       <c r="C43" t="s">
         <v>3</v>
       </c>
@@ -13754,6 +17556,8 @@
       <c r="K43">
         <v>16</v>
       </c>
+      <c r="L43" s="2"/>
+      <c r="M43" s="2"/>
       <c r="O43" t="s">
         <v>3</v>
       </c>
@@ -13775,6 +17579,8 @@
       <c r="W43">
         <v>8</v>
       </c>
+      <c r="X43" s="3"/>
+      <c r="Y43" s="3"/>
       <c r="AA43" t="s">
         <v>3</v>
       </c>
@@ -13784,8 +17590,20 @@
       <c r="AC43">
         <v>30</v>
       </c>
+      <c r="AE43">
+        <v>4206</v>
+      </c>
+      <c r="AF43">
+        <v>29</v>
+      </c>
+      <c r="AH43">
+        <v>3807</v>
+      </c>
+      <c r="AI43">
+        <v>27</v>
+      </c>
     </row>
-    <row r="44" spans="2:29" x14ac:dyDescent="0.35">
+    <row r="44" spans="2:35" x14ac:dyDescent="0.35">
       <c r="C44" t="s">
         <v>4</v>
       </c>
@@ -13807,6 +17625,8 @@
       <c r="K44">
         <v>17</v>
       </c>
+      <c r="L44" s="2"/>
+      <c r="M44" s="2"/>
       <c r="O44" t="s">
         <v>4</v>
       </c>
@@ -13828,6 +17648,8 @@
       <c r="W44">
         <v>15</v>
       </c>
+      <c r="X44" s="3"/>
+      <c r="Y44" s="3"/>
       <c r="AA44" t="s">
         <v>4</v>
       </c>
@@ -13837,8 +17659,20 @@
       <c r="AC44">
         <v>24</v>
       </c>
+      <c r="AE44">
+        <v>4144</v>
+      </c>
+      <c r="AF44">
+        <v>27</v>
+      </c>
+      <c r="AH44">
+        <v>3768</v>
+      </c>
+      <c r="AI44">
+        <v>29</v>
+      </c>
     </row>
-    <row r="45" spans="2:29" x14ac:dyDescent="0.35">
+    <row r="45" spans="2:35" x14ac:dyDescent="0.35">
       <c r="C45" t="s">
         <v>5</v>
       </c>
@@ -13860,6 +17694,8 @@
       <c r="K45">
         <v>17</v>
       </c>
+      <c r="L45" s="2"/>
+      <c r="M45" s="2"/>
       <c r="O45" t="s">
         <v>5</v>
       </c>
@@ -13881,6 +17717,8 @@
       <c r="W45">
         <v>8</v>
       </c>
+      <c r="X45" s="3"/>
+      <c r="Y45" s="3"/>
       <c r="AA45" t="s">
         <v>5</v>
       </c>
@@ -13890,19 +17728,35 @@
       <c r="AC45">
         <v>27</v>
       </c>
+      <c r="AE45">
+        <v>4033</v>
+      </c>
+      <c r="AF45">
+        <v>29</v>
+      </c>
+      <c r="AH45">
+        <v>3751</v>
+      </c>
+      <c r="AI45">
+        <v>28</v>
+      </c>
     </row>
-    <row r="46" spans="2:29" x14ac:dyDescent="0.35">
+    <row r="46" spans="2:35" x14ac:dyDescent="0.35">
       <c r="B46" t="s">
         <v>12</v>
       </c>
+      <c r="L46" s="2"/>
+      <c r="M46" s="2"/>
       <c r="N46" t="s">
         <v>12</v>
       </c>
+      <c r="X46" s="3"/>
+      <c r="Y46" s="3"/>
       <c r="Z46" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="47" spans="2:29" x14ac:dyDescent="0.35">
+    <row r="47" spans="2:35" x14ac:dyDescent="0.35">
       <c r="C47" t="s">
         <v>1</v>
       </c>
@@ -13924,6 +17778,8 @@
       <c r="K47">
         <v>20</v>
       </c>
+      <c r="L47" s="2"/>
+      <c r="M47" s="2"/>
       <c r="O47" t="s">
         <v>1</v>
       </c>
@@ -13945,6 +17801,8 @@
       <c r="W47">
         <v>11</v>
       </c>
+      <c r="X47" s="3"/>
+      <c r="Y47" s="3"/>
       <c r="AA47" t="s">
         <v>1</v>
       </c>
@@ -13954,8 +17812,20 @@
       <c r="AC47">
         <v>27</v>
       </c>
+      <c r="AE47">
+        <v>4155</v>
+      </c>
+      <c r="AF47">
+        <v>26</v>
+      </c>
+      <c r="AH47">
+        <v>3772</v>
+      </c>
+      <c r="AI47">
+        <v>28</v>
+      </c>
     </row>
-    <row r="48" spans="2:29" x14ac:dyDescent="0.35">
+    <row r="48" spans="2:35" x14ac:dyDescent="0.35">
       <c r="C48" t="s">
         <v>2</v>
       </c>
@@ -13977,6 +17847,8 @@
       <c r="K48">
         <v>19</v>
       </c>
+      <c r="L48" s="2"/>
+      <c r="M48" s="2"/>
       <c r="O48" t="s">
         <v>2</v>
       </c>
@@ -13998,6 +17870,8 @@
       <c r="W48">
         <v>6</v>
       </c>
+      <c r="X48" s="3"/>
+      <c r="Y48" s="3"/>
       <c r="AA48" t="s">
         <v>2</v>
       </c>
@@ -14007,8 +17881,20 @@
       <c r="AC48">
         <v>30</v>
       </c>
+      <c r="AE48">
+        <v>4250</v>
+      </c>
+      <c r="AF48">
+        <v>29</v>
+      </c>
+      <c r="AH48">
+        <v>3787</v>
+      </c>
+      <c r="AI48">
+        <v>29</v>
+      </c>
     </row>
-    <row r="49" spans="2:29" x14ac:dyDescent="0.35">
+    <row r="49" spans="2:35" x14ac:dyDescent="0.35">
       <c r="C49" t="s">
         <v>3</v>
       </c>
@@ -14030,6 +17916,8 @@
       <c r="K49">
         <v>19</v>
       </c>
+      <c r="L49" s="2"/>
+      <c r="M49" s="2"/>
       <c r="O49" t="s">
         <v>3</v>
       </c>
@@ -14051,6 +17939,8 @@
       <c r="W49">
         <v>11</v>
       </c>
+      <c r="X49" s="3"/>
+      <c r="Y49" s="3"/>
       <c r="AA49" t="s">
         <v>3</v>
       </c>
@@ -14060,8 +17950,20 @@
       <c r="AC49">
         <v>28</v>
       </c>
+      <c r="AE49">
+        <v>4098</v>
+      </c>
+      <c r="AF49">
+        <v>29</v>
+      </c>
+      <c r="AH49">
+        <v>3750</v>
+      </c>
+      <c r="AI49">
+        <v>28</v>
+      </c>
     </row>
-    <row r="50" spans="2:29" x14ac:dyDescent="0.35">
+    <row r="50" spans="2:35" x14ac:dyDescent="0.35">
       <c r="C50" t="s">
         <v>4</v>
       </c>
@@ -14083,6 +17985,8 @@
       <c r="K50">
         <v>18</v>
       </c>
+      <c r="L50" s="2"/>
+      <c r="M50" s="2"/>
       <c r="O50" t="s">
         <v>4</v>
       </c>
@@ -14104,6 +18008,8 @@
       <c r="W50">
         <v>9</v>
       </c>
+      <c r="X50" s="3"/>
+      <c r="Y50" s="3"/>
       <c r="AA50" t="s">
         <v>4</v>
       </c>
@@ -14113,8 +18019,20 @@
       <c r="AC50">
         <v>27</v>
       </c>
+      <c r="AE50">
+        <v>4242</v>
+      </c>
+      <c r="AF50">
+        <v>30</v>
+      </c>
+      <c r="AH50">
+        <v>3774</v>
+      </c>
+      <c r="AI50">
+        <v>29</v>
+      </c>
     </row>
-    <row r="51" spans="2:29" x14ac:dyDescent="0.35">
+    <row r="51" spans="2:35" x14ac:dyDescent="0.35">
       <c r="C51" t="s">
         <v>5</v>
       </c>
@@ -14136,6 +18054,8 @@
       <c r="K51">
         <v>11</v>
       </c>
+      <c r="L51" s="2"/>
+      <c r="M51" s="2"/>
       <c r="O51" t="s">
         <v>5</v>
       </c>
@@ -14157,6 +18077,8 @@
       <c r="W51">
         <v>13</v>
       </c>
+      <c r="X51" s="3"/>
+      <c r="Y51" s="3"/>
       <c r="AA51" t="s">
         <v>5</v>
       </c>
@@ -14166,19 +18088,35 @@
       <c r="AC51">
         <v>24</v>
       </c>
+      <c r="AE51">
+        <v>4345</v>
+      </c>
+      <c r="AF51">
+        <v>29</v>
+      </c>
+      <c r="AH51">
+        <v>3756</v>
+      </c>
+      <c r="AI51">
+        <v>29</v>
+      </c>
     </row>
-    <row r="52" spans="2:29" x14ac:dyDescent="0.35">
+    <row r="52" spans="2:35" x14ac:dyDescent="0.35">
       <c r="B52" t="s">
         <v>13</v>
       </c>
+      <c r="L52" s="2"/>
+      <c r="M52" s="2"/>
       <c r="N52" t="s">
         <v>13</v>
       </c>
+      <c r="X52" s="3"/>
+      <c r="Y52" s="3"/>
       <c r="Z52" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="53" spans="2:29" x14ac:dyDescent="0.35">
+    <row r="53" spans="2:35" x14ac:dyDescent="0.35">
       <c r="C53" t="s">
         <v>1</v>
       </c>
@@ -14200,6 +18138,8 @@
       <c r="K53">
         <v>21</v>
       </c>
+      <c r="L53" s="2"/>
+      <c r="M53" s="2"/>
       <c r="O53" t="s">
         <v>1</v>
       </c>
@@ -14221,6 +18161,8 @@
       <c r="W53">
         <v>4</v>
       </c>
+      <c r="X53" s="3"/>
+      <c r="Y53" s="3"/>
       <c r="AA53" t="s">
         <v>1</v>
       </c>
@@ -14230,8 +18172,20 @@
       <c r="AC53">
         <v>29</v>
       </c>
+      <c r="AE53">
+        <v>4159</v>
+      </c>
+      <c r="AF53">
+        <v>29</v>
+      </c>
+      <c r="AH53">
+        <v>3812</v>
+      </c>
+      <c r="AI53">
+        <v>29</v>
+      </c>
     </row>
-    <row r="54" spans="2:29" x14ac:dyDescent="0.35">
+    <row r="54" spans="2:35" x14ac:dyDescent="0.35">
       <c r="C54" t="s">
         <v>2</v>
       </c>
@@ -14253,6 +18207,8 @@
       <c r="K54">
         <v>20</v>
       </c>
+      <c r="L54" s="2"/>
+      <c r="M54" s="2"/>
       <c r="O54" t="s">
         <v>2</v>
       </c>
@@ -14274,6 +18230,8 @@
       <c r="W54">
         <v>7</v>
       </c>
+      <c r="X54" s="3"/>
+      <c r="Y54" s="3"/>
       <c r="AA54" t="s">
         <v>2</v>
       </c>
@@ -14283,8 +18241,20 @@
       <c r="AC54">
         <v>26</v>
       </c>
+      <c r="AE54">
+        <v>4111</v>
+      </c>
+      <c r="AF54">
+        <v>27</v>
+      </c>
+      <c r="AH54">
+        <v>3761</v>
+      </c>
+      <c r="AI54">
+        <v>30</v>
+      </c>
     </row>
-    <row r="55" spans="2:29" x14ac:dyDescent="0.35">
+    <row r="55" spans="2:35" x14ac:dyDescent="0.35">
       <c r="C55" t="s">
         <v>3</v>
       </c>
@@ -14306,6 +18276,8 @@
       <c r="K55">
         <v>17</v>
       </c>
+      <c r="L55" s="2"/>
+      <c r="M55" s="2"/>
       <c r="O55" t="s">
         <v>3</v>
       </c>
@@ -14327,6 +18299,8 @@
       <c r="W55">
         <v>9</v>
       </c>
+      <c r="X55" s="3"/>
+      <c r="Y55" s="3"/>
       <c r="AA55" t="s">
         <v>3</v>
       </c>
@@ -14336,8 +18310,20 @@
       <c r="AC55">
         <v>28</v>
       </c>
+      <c r="AE55">
+        <v>4102</v>
+      </c>
+      <c r="AF55">
+        <v>28</v>
+      </c>
+      <c r="AH55">
+        <v>3770</v>
+      </c>
+      <c r="AI55">
+        <v>28</v>
+      </c>
     </row>
-    <row r="56" spans="2:29" x14ac:dyDescent="0.35">
+    <row r="56" spans="2:35" x14ac:dyDescent="0.35">
       <c r="C56" t="s">
         <v>4</v>
       </c>
@@ -14359,6 +18345,8 @@
       <c r="K56">
         <v>12</v>
       </c>
+      <c r="L56" s="2"/>
+      <c r="M56" s="2"/>
       <c r="O56" t="s">
         <v>4</v>
       </c>
@@ -14380,6 +18368,8 @@
       <c r="W56">
         <v>2</v>
       </c>
+      <c r="X56" s="3"/>
+      <c r="Y56" s="3"/>
       <c r="AA56" t="s">
         <v>4</v>
       </c>
@@ -14389,8 +18379,20 @@
       <c r="AC56">
         <v>30</v>
       </c>
+      <c r="AE56">
+        <v>4161</v>
+      </c>
+      <c r="AF56">
+        <v>29</v>
+      </c>
+      <c r="AH56">
+        <v>3778</v>
+      </c>
+      <c r="AI56">
+        <v>29</v>
+      </c>
     </row>
-    <row r="57" spans="2:29" x14ac:dyDescent="0.35">
+    <row r="57" spans="2:35" x14ac:dyDescent="0.35">
       <c r="C57" t="s">
         <v>5</v>
       </c>
@@ -14412,6 +18414,8 @@
       <c r="K57">
         <v>14</v>
       </c>
+      <c r="L57" s="2"/>
+      <c r="M57" s="2"/>
       <c r="O57" t="s">
         <v>5</v>
       </c>
@@ -14433,6 +18437,8 @@
       <c r="W57">
         <v>13</v>
       </c>
+      <c r="X57" s="3"/>
+      <c r="Y57" s="3"/>
       <c r="AA57" t="s">
         <v>5</v>
       </c>
@@ -14442,19 +18448,35 @@
       <c r="AC57">
         <v>27</v>
       </c>
+      <c r="AE57">
+        <v>4168</v>
+      </c>
+      <c r="AF57">
+        <v>28</v>
+      </c>
+      <c r="AH57">
+        <v>3757</v>
+      </c>
+      <c r="AI57">
+        <v>29</v>
+      </c>
     </row>
-    <row r="58" spans="2:29" x14ac:dyDescent="0.35">
+    <row r="58" spans="2:35" x14ac:dyDescent="0.35">
       <c r="B58" t="s">
         <v>14</v>
       </c>
+      <c r="L58" s="2"/>
+      <c r="M58" s="2"/>
       <c r="N58" t="s">
         <v>14</v>
       </c>
+      <c r="X58" s="3"/>
+      <c r="Y58" s="3"/>
       <c r="Z58" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="59" spans="2:29" x14ac:dyDescent="0.35">
+    <row r="59" spans="2:35" x14ac:dyDescent="0.35">
       <c r="C59" t="s">
         <v>1</v>
       </c>
@@ -14476,6 +18498,8 @@
       <c r="K59">
         <v>16</v>
       </c>
+      <c r="L59" s="2"/>
+      <c r="M59" s="2"/>
       <c r="O59" t="s">
         <v>1</v>
       </c>
@@ -14497,6 +18521,8 @@
       <c r="W59">
         <v>9</v>
       </c>
+      <c r="X59" s="3"/>
+      <c r="Y59" s="3"/>
       <c r="AA59" t="s">
         <v>1</v>
       </c>
@@ -14506,8 +18532,20 @@
       <c r="AC59">
         <v>29</v>
       </c>
+      <c r="AE59">
+        <v>4030</v>
+      </c>
+      <c r="AF59">
+        <v>24</v>
+      </c>
+      <c r="AH59">
+        <v>3748</v>
+      </c>
+      <c r="AI59">
+        <v>29</v>
+      </c>
     </row>
-    <row r="60" spans="2:29" x14ac:dyDescent="0.35">
+    <row r="60" spans="2:35" x14ac:dyDescent="0.35">
       <c r="C60" t="s">
         <v>2</v>
       </c>
@@ -14529,6 +18567,8 @@
       <c r="K60">
         <v>18</v>
       </c>
+      <c r="L60" s="2"/>
+      <c r="M60" s="2"/>
       <c r="O60" t="s">
         <v>2</v>
       </c>
@@ -14550,6 +18590,8 @@
       <c r="W60">
         <v>7</v>
       </c>
+      <c r="X60" s="3"/>
+      <c r="Y60" s="3"/>
       <c r="AA60" t="s">
         <v>2</v>
       </c>
@@ -14559,8 +18601,20 @@
       <c r="AC60">
         <v>28</v>
       </c>
+      <c r="AE60">
+        <v>4107</v>
+      </c>
+      <c r="AF60">
+        <v>30</v>
+      </c>
+      <c r="AH60">
+        <v>3770</v>
+      </c>
+      <c r="AI60">
+        <v>28</v>
+      </c>
     </row>
-    <row r="61" spans="2:29" x14ac:dyDescent="0.35">
+    <row r="61" spans="2:35" x14ac:dyDescent="0.35">
       <c r="C61" t="s">
         <v>3</v>
       </c>
@@ -14582,6 +18636,8 @@
       <c r="K61">
         <v>25</v>
       </c>
+      <c r="L61" s="2"/>
+      <c r="M61" s="2"/>
       <c r="O61" t="s">
         <v>3</v>
       </c>
@@ -14603,6 +18659,8 @@
       <c r="W61">
         <v>11</v>
       </c>
+      <c r="X61" s="3"/>
+      <c r="Y61" s="3"/>
       <c r="AA61" t="s">
         <v>3</v>
       </c>
@@ -14612,8 +18670,20 @@
       <c r="AC61">
         <v>28</v>
       </c>
+      <c r="AE61">
+        <v>4126</v>
+      </c>
+      <c r="AF61">
+        <v>26</v>
+      </c>
+      <c r="AH61">
+        <v>3763</v>
+      </c>
+      <c r="AI61">
+        <v>27</v>
+      </c>
     </row>
-    <row r="62" spans="2:29" x14ac:dyDescent="0.35">
+    <row r="62" spans="2:35" x14ac:dyDescent="0.35">
       <c r="C62" t="s">
         <v>4</v>
       </c>
@@ -14635,6 +18705,8 @@
       <c r="K62">
         <v>14</v>
       </c>
+      <c r="L62" s="2"/>
+      <c r="M62" s="2"/>
       <c r="O62" t="s">
         <v>4</v>
       </c>
@@ -14656,6 +18728,8 @@
       <c r="W62">
         <v>7</v>
       </c>
+      <c r="X62" s="3"/>
+      <c r="Y62" s="3"/>
       <c r="AA62" t="s">
         <v>4</v>
       </c>
@@ -14665,8 +18739,20 @@
       <c r="AC62">
         <v>29</v>
       </c>
+      <c r="AE62">
+        <v>4068</v>
+      </c>
+      <c r="AF62">
+        <v>28</v>
+      </c>
+      <c r="AH62">
+        <v>3798</v>
+      </c>
+      <c r="AI62">
+        <v>23</v>
+      </c>
     </row>
-    <row r="63" spans="2:29" x14ac:dyDescent="0.35">
+    <row r="63" spans="2:35" x14ac:dyDescent="0.35">
       <c r="C63" t="s">
         <v>5</v>
       </c>
@@ -14688,6 +18774,8 @@
       <c r="K63">
         <v>13</v>
       </c>
+      <c r="L63" s="2"/>
+      <c r="M63" s="2"/>
       <c r="O63" t="s">
         <v>5</v>
       </c>
@@ -14709,6 +18797,8 @@
       <c r="W63">
         <v>6</v>
       </c>
+      <c r="X63" s="3"/>
+      <c r="Y63" s="3"/>
       <c r="AA63" t="s">
         <v>5</v>
       </c>
@@ -14718,19 +18808,35 @@
       <c r="AC63">
         <v>27</v>
       </c>
+      <c r="AE63">
+        <v>4038</v>
+      </c>
+      <c r="AF63">
+        <v>30</v>
+      </c>
+      <c r="AH63">
+        <v>3771</v>
+      </c>
+      <c r="AI63">
+        <v>28</v>
+      </c>
     </row>
-    <row r="64" spans="2:29" x14ac:dyDescent="0.35">
+    <row r="64" spans="2:35" x14ac:dyDescent="0.35">
       <c r="B64" t="s">
         <v>15</v>
       </c>
+      <c r="L64" s="2"/>
+      <c r="M64" s="2"/>
       <c r="N64" t="s">
         <v>15</v>
       </c>
+      <c r="X64" s="3"/>
+      <c r="Y64" s="3"/>
       <c r="Z64" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="65" spans="2:29" x14ac:dyDescent="0.35">
+    <row r="65" spans="2:35" x14ac:dyDescent="0.35">
       <c r="C65" t="s">
         <v>1</v>
       </c>
@@ -14752,6 +18858,8 @@
       <c r="K65">
         <v>20</v>
       </c>
+      <c r="L65" s="2"/>
+      <c r="M65" s="2"/>
       <c r="O65" t="s">
         <v>1</v>
       </c>
@@ -14773,6 +18881,8 @@
       <c r="W65">
         <v>8</v>
       </c>
+      <c r="X65" s="3"/>
+      <c r="Y65" s="3"/>
       <c r="AA65" t="s">
         <v>1</v>
       </c>
@@ -14782,8 +18892,20 @@
       <c r="AC65">
         <v>29</v>
       </c>
+      <c r="AE65">
+        <v>4220</v>
+      </c>
+      <c r="AF65">
+        <v>30</v>
+      </c>
+      <c r="AH65">
+        <v>3773</v>
+      </c>
+      <c r="AI65">
+        <v>30</v>
+      </c>
     </row>
-    <row r="66" spans="2:29" x14ac:dyDescent="0.35">
+    <row r="66" spans="2:35" x14ac:dyDescent="0.35">
       <c r="C66" t="s">
         <v>2</v>
       </c>
@@ -14805,6 +18927,8 @@
       <c r="K66">
         <v>16</v>
       </c>
+      <c r="L66" s="2"/>
+      <c r="M66" s="2"/>
       <c r="O66" t="s">
         <v>2</v>
       </c>
@@ -14826,6 +18950,8 @@
       <c r="W66">
         <v>13</v>
       </c>
+      <c r="X66" s="3"/>
+      <c r="Y66" s="3"/>
       <c r="AA66" t="s">
         <v>2</v>
       </c>
@@ -14835,8 +18961,20 @@
       <c r="AC66">
         <v>28</v>
       </c>
+      <c r="AE66">
+        <v>4389</v>
+      </c>
+      <c r="AF66">
+        <v>29</v>
+      </c>
+      <c r="AH66">
+        <v>3783</v>
+      </c>
+      <c r="AI66">
+        <v>28</v>
+      </c>
     </row>
-    <row r="67" spans="2:29" x14ac:dyDescent="0.35">
+    <row r="67" spans="2:35" x14ac:dyDescent="0.35">
       <c r="C67" t="s">
         <v>3</v>
       </c>
@@ -14858,6 +18996,8 @@
       <c r="K67">
         <v>20</v>
       </c>
+      <c r="L67" s="2"/>
+      <c r="M67" s="2"/>
       <c r="O67" t="s">
         <v>3</v>
       </c>
@@ -14879,6 +19019,8 @@
       <c r="W67">
         <v>7</v>
       </c>
+      <c r="X67" s="3"/>
+      <c r="Y67" s="3"/>
       <c r="AA67" t="s">
         <v>3</v>
       </c>
@@ -14888,8 +19030,20 @@
       <c r="AC67">
         <v>29</v>
       </c>
+      <c r="AE67">
+        <v>4210</v>
+      </c>
+      <c r="AF67">
+        <v>30</v>
+      </c>
+      <c r="AH67">
+        <v>3774</v>
+      </c>
+      <c r="AI67">
+        <v>28</v>
+      </c>
     </row>
-    <row r="68" spans="2:29" x14ac:dyDescent="0.35">
+    <row r="68" spans="2:35" x14ac:dyDescent="0.35">
       <c r="C68" t="s">
         <v>4</v>
       </c>
@@ -14911,6 +19065,8 @@
       <c r="K68">
         <v>16</v>
       </c>
+      <c r="L68" s="2"/>
+      <c r="M68" s="2"/>
       <c r="O68" t="s">
         <v>4</v>
       </c>
@@ -14932,6 +19088,8 @@
       <c r="W68">
         <v>9</v>
       </c>
+      <c r="X68" s="3"/>
+      <c r="Y68" s="3"/>
       <c r="AA68" t="s">
         <v>4</v>
       </c>
@@ -14941,8 +19099,20 @@
       <c r="AC68">
         <v>28</v>
       </c>
+      <c r="AE68">
+        <v>4331</v>
+      </c>
+      <c r="AF68">
+        <v>29</v>
+      </c>
+      <c r="AH68">
+        <v>3802</v>
+      </c>
+      <c r="AI68">
+        <v>29</v>
+      </c>
     </row>
-    <row r="69" spans="2:29" x14ac:dyDescent="0.35">
+    <row r="69" spans="2:35" x14ac:dyDescent="0.35">
       <c r="C69" t="s">
         <v>5</v>
       </c>
@@ -14964,6 +19134,8 @@
       <c r="K69">
         <v>22</v>
       </c>
+      <c r="L69" s="2"/>
+      <c r="M69" s="2"/>
       <c r="O69" t="s">
         <v>5</v>
       </c>
@@ -14985,6 +19157,8 @@
       <c r="W69">
         <v>10</v>
       </c>
+      <c r="X69" s="3"/>
+      <c r="Y69" s="3"/>
       <c r="AA69" t="s">
         <v>5</v>
       </c>
@@ -14994,19 +19168,35 @@
       <c r="AC69">
         <v>29</v>
       </c>
+      <c r="AE69">
+        <v>4196</v>
+      </c>
+      <c r="AF69">
+        <v>28</v>
+      </c>
+      <c r="AH69">
+        <v>3774</v>
+      </c>
+      <c r="AI69">
+        <v>30</v>
+      </c>
     </row>
-    <row r="70" spans="2:29" x14ac:dyDescent="0.35">
+    <row r="70" spans="2:35" x14ac:dyDescent="0.35">
       <c r="B70" t="s">
         <v>16</v>
       </c>
+      <c r="L70" s="2"/>
+      <c r="M70" s="2"/>
       <c r="N70" t="s">
         <v>16</v>
       </c>
+      <c r="X70" s="3"/>
+      <c r="Y70" s="3"/>
       <c r="Z70" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="71" spans="2:29" x14ac:dyDescent="0.35">
+    <row r="71" spans="2:35" x14ac:dyDescent="0.35">
       <c r="C71" t="s">
         <v>1</v>
       </c>
@@ -15028,6 +19218,8 @@
       <c r="K71">
         <v>18</v>
       </c>
+      <c r="L71" s="2"/>
+      <c r="M71" s="2"/>
       <c r="O71" t="s">
         <v>1</v>
       </c>
@@ -15049,6 +19241,8 @@
       <c r="W71">
         <v>10</v>
       </c>
+      <c r="X71" s="3"/>
+      <c r="Y71" s="3"/>
       <c r="AA71" t="s">
         <v>1</v>
       </c>
@@ -15058,8 +19252,20 @@
       <c r="AC71">
         <v>28</v>
       </c>
+      <c r="AE71">
+        <v>4106</v>
+      </c>
+      <c r="AF71">
+        <v>27</v>
+      </c>
+      <c r="AH71">
+        <v>3751</v>
+      </c>
+      <c r="AI71">
+        <v>28</v>
+      </c>
     </row>
-    <row r="72" spans="2:29" x14ac:dyDescent="0.35">
+    <row r="72" spans="2:35" x14ac:dyDescent="0.35">
       <c r="C72" t="s">
         <v>2</v>
       </c>
@@ -15081,6 +19287,8 @@
       <c r="K72">
         <v>10</v>
       </c>
+      <c r="L72" s="2"/>
+      <c r="M72" s="2"/>
       <c r="O72" t="s">
         <v>2</v>
       </c>
@@ -15102,6 +19310,8 @@
       <c r="W72">
         <v>12</v>
       </c>
+      <c r="X72" s="3"/>
+      <c r="Y72" s="3"/>
       <c r="AA72" t="s">
         <v>2</v>
       </c>
@@ -15111,8 +19321,20 @@
       <c r="AC72">
         <v>29</v>
       </c>
+      <c r="AE72">
+        <v>4161</v>
+      </c>
+      <c r="AF72">
+        <v>28</v>
+      </c>
+      <c r="AH72">
+        <v>3754</v>
+      </c>
+      <c r="AI72">
+        <v>30</v>
+      </c>
     </row>
-    <row r="73" spans="2:29" x14ac:dyDescent="0.35">
+    <row r="73" spans="2:35" x14ac:dyDescent="0.35">
       <c r="C73" t="s">
         <v>3</v>
       </c>
@@ -15134,6 +19356,8 @@
       <c r="K73">
         <v>18</v>
       </c>
+      <c r="L73" s="2"/>
+      <c r="M73" s="2"/>
       <c r="O73" t="s">
         <v>3</v>
       </c>
@@ -15155,6 +19379,8 @@
       <c r="W73">
         <v>10</v>
       </c>
+      <c r="X73" s="3"/>
+      <c r="Y73" s="3"/>
       <c r="AA73" t="s">
         <v>3</v>
       </c>
@@ -15164,8 +19390,20 @@
       <c r="AC73">
         <v>29</v>
       </c>
+      <c r="AE73">
+        <v>4077</v>
+      </c>
+      <c r="AF73">
+        <v>28</v>
+      </c>
+      <c r="AH73">
+        <v>3754</v>
+      </c>
+      <c r="AI73">
+        <v>29</v>
+      </c>
     </row>
-    <row r="74" spans="2:29" x14ac:dyDescent="0.35">
+    <row r="74" spans="2:35" x14ac:dyDescent="0.35">
       <c r="C74" t="s">
         <v>4</v>
       </c>
@@ -15187,6 +19425,8 @@
       <c r="K74">
         <v>23</v>
       </c>
+      <c r="L74" s="2"/>
+      <c r="M74" s="2"/>
       <c r="O74" t="s">
         <v>4</v>
       </c>
@@ -15208,6 +19448,8 @@
       <c r="W74">
         <v>4</v>
       </c>
+      <c r="X74" s="3"/>
+      <c r="Y74" s="3"/>
       <c r="AA74" t="s">
         <v>4</v>
       </c>
@@ -15217,8 +19459,20 @@
       <c r="AC74">
         <v>28</v>
       </c>
+      <c r="AE74">
+        <v>4082</v>
+      </c>
+      <c r="AF74">
+        <v>28</v>
+      </c>
+      <c r="AH74">
+        <v>3796</v>
+      </c>
+      <c r="AI74">
+        <v>26</v>
+      </c>
     </row>
-    <row r="75" spans="2:29" x14ac:dyDescent="0.35">
+    <row r="75" spans="2:35" x14ac:dyDescent="0.35">
       <c r="C75" t="s">
         <v>5</v>
       </c>
@@ -15240,6 +19494,8 @@
       <c r="K75">
         <v>21</v>
       </c>
+      <c r="L75" s="2"/>
+      <c r="M75" s="2"/>
       <c r="O75" t="s">
         <v>5</v>
       </c>
@@ -15261,6 +19517,8 @@
       <c r="W75">
         <v>9</v>
       </c>
+      <c r="X75" s="3"/>
+      <c r="Y75" s="3"/>
       <c r="AA75" t="s">
         <v>5</v>
       </c>
@@ -15270,19 +19528,35 @@
       <c r="AC75">
         <v>27</v>
       </c>
+      <c r="AE75">
+        <v>4078</v>
+      </c>
+      <c r="AF75">
+        <v>26</v>
+      </c>
+      <c r="AH75">
+        <v>3878</v>
+      </c>
+      <c r="AI75">
+        <v>28</v>
+      </c>
     </row>
-    <row r="76" spans="2:29" x14ac:dyDescent="0.35">
+    <row r="76" spans="2:35" x14ac:dyDescent="0.35">
       <c r="B76" t="s">
         <v>17</v>
       </c>
+      <c r="L76" s="2"/>
+      <c r="M76" s="2"/>
       <c r="N76" t="s">
         <v>17</v>
       </c>
+      <c r="X76" s="3"/>
+      <c r="Y76" s="3"/>
       <c r="Z76" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="77" spans="2:29" x14ac:dyDescent="0.35">
+    <row r="77" spans="2:35" x14ac:dyDescent="0.35">
       <c r="C77" t="s">
         <v>1</v>
       </c>
@@ -15304,6 +19578,8 @@
       <c r="K77">
         <v>17</v>
       </c>
+      <c r="L77" s="2"/>
+      <c r="M77" s="2"/>
       <c r="O77" t="s">
         <v>1</v>
       </c>
@@ -15325,6 +19601,8 @@
       <c r="W77">
         <v>6</v>
       </c>
+      <c r="X77" s="3"/>
+      <c r="Y77" s="3"/>
       <c r="AA77" t="s">
         <v>1</v>
       </c>
@@ -15334,8 +19612,20 @@
       <c r="AC77">
         <v>26</v>
       </c>
+      <c r="AE77">
+        <v>4032</v>
+      </c>
+      <c r="AF77">
+        <v>28</v>
+      </c>
+      <c r="AH77">
+        <v>3754</v>
+      </c>
+      <c r="AI77">
+        <v>27</v>
+      </c>
     </row>
-    <row r="78" spans="2:29" x14ac:dyDescent="0.35">
+    <row r="78" spans="2:35" x14ac:dyDescent="0.35">
       <c r="C78" t="s">
         <v>2</v>
       </c>
@@ -15357,6 +19647,8 @@
       <c r="K78">
         <v>15</v>
       </c>
+      <c r="L78" s="2"/>
+      <c r="M78" s="2"/>
       <c r="O78" t="s">
         <v>2</v>
       </c>
@@ -15378,6 +19670,8 @@
       <c r="W78">
         <v>10</v>
       </c>
+      <c r="X78" s="3"/>
+      <c r="Y78" s="3"/>
       <c r="AA78" t="s">
         <v>2</v>
       </c>
@@ -15387,8 +19681,20 @@
       <c r="AC78">
         <v>27</v>
       </c>
+      <c r="AE78">
+        <v>4052</v>
+      </c>
+      <c r="AF78">
+        <v>28</v>
+      </c>
+      <c r="AH78">
+        <v>3750</v>
+      </c>
+      <c r="AI78">
+        <v>28</v>
+      </c>
     </row>
-    <row r="79" spans="2:29" x14ac:dyDescent="0.35">
+    <row r="79" spans="2:35" x14ac:dyDescent="0.35">
       <c r="C79" t="s">
         <v>3</v>
       </c>
@@ -15410,6 +19716,8 @@
       <c r="K79">
         <v>16</v>
       </c>
+      <c r="L79" s="2"/>
+      <c r="M79" s="2"/>
       <c r="O79" t="s">
         <v>3</v>
       </c>
@@ -15431,6 +19739,8 @@
       <c r="W79">
         <v>10</v>
       </c>
+      <c r="X79" s="3"/>
+      <c r="Y79" s="3"/>
       <c r="AA79" t="s">
         <v>3</v>
       </c>
@@ -15440,8 +19750,20 @@
       <c r="AC79">
         <v>30</v>
       </c>
+      <c r="AE79">
+        <v>4055</v>
+      </c>
+      <c r="AF79">
+        <v>28</v>
+      </c>
+      <c r="AH79">
+        <v>3759</v>
+      </c>
+      <c r="AI79">
+        <v>29</v>
+      </c>
     </row>
-    <row r="80" spans="2:29" x14ac:dyDescent="0.35">
+    <row r="80" spans="2:35" x14ac:dyDescent="0.35">
       <c r="C80" t="s">
         <v>4</v>
       </c>
@@ -15463,6 +19785,8 @@
       <c r="K80">
         <v>11</v>
       </c>
+      <c r="L80" s="2"/>
+      <c r="M80" s="2"/>
       <c r="O80" t="s">
         <v>4</v>
       </c>
@@ -15484,6 +19808,8 @@
       <c r="W80">
         <v>11</v>
       </c>
+      <c r="X80" s="3"/>
+      <c r="Y80" s="3"/>
       <c r="AA80" t="s">
         <v>4</v>
       </c>
@@ -15493,8 +19819,20 @@
       <c r="AC80">
         <v>28</v>
       </c>
+      <c r="AE80">
+        <v>4076</v>
+      </c>
+      <c r="AF80">
+        <v>27</v>
+      </c>
+      <c r="AH80">
+        <v>4233</v>
+      </c>
+      <c r="AI80">
+        <v>25</v>
+      </c>
     </row>
-    <row r="81" spans="2:29" x14ac:dyDescent="0.35">
+    <row r="81" spans="2:35" x14ac:dyDescent="0.35">
       <c r="C81" t="s">
         <v>5</v>
       </c>
@@ -15516,6 +19854,8 @@
       <c r="K81">
         <v>11</v>
       </c>
+      <c r="L81" s="2"/>
+      <c r="M81" s="2"/>
       <c r="O81" t="s">
         <v>5</v>
       </c>
@@ -15537,6 +19877,8 @@
       <c r="W81">
         <v>13</v>
       </c>
+      <c r="X81" s="3"/>
+      <c r="Y81" s="3"/>
       <c r="AA81" t="s">
         <v>5</v>
       </c>
@@ -15546,19 +19888,35 @@
       <c r="AC81">
         <v>30</v>
       </c>
+      <c r="AE81">
+        <v>4071</v>
+      </c>
+      <c r="AF81">
+        <v>29</v>
+      </c>
+      <c r="AH81">
+        <v>4450</v>
+      </c>
+      <c r="AI81">
+        <v>28</v>
+      </c>
     </row>
-    <row r="82" spans="2:29" x14ac:dyDescent="0.35">
+    <row r="82" spans="2:35" x14ac:dyDescent="0.35">
       <c r="B82" t="s">
         <v>18</v>
       </c>
+      <c r="L82" s="2"/>
+      <c r="M82" s="2"/>
       <c r="N82" t="s">
         <v>18</v>
       </c>
+      <c r="X82" s="3"/>
+      <c r="Y82" s="3"/>
       <c r="Z82" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="83" spans="2:29" x14ac:dyDescent="0.35">
+    <row r="83" spans="2:35" x14ac:dyDescent="0.35">
       <c r="C83" t="s">
         <v>1</v>
       </c>
@@ -15580,6 +19938,8 @@
       <c r="K83">
         <v>23</v>
       </c>
+      <c r="L83" s="2"/>
+      <c r="M83" s="2"/>
       <c r="O83" t="s">
         <v>1</v>
       </c>
@@ -15601,6 +19961,8 @@
       <c r="W83">
         <v>10</v>
       </c>
+      <c r="X83" s="3"/>
+      <c r="Y83" s="3"/>
       <c r="AA83" t="s">
         <v>1</v>
       </c>
@@ -15610,8 +19972,20 @@
       <c r="AC83">
         <v>29</v>
       </c>
+      <c r="AE83">
+        <v>4209</v>
+      </c>
+      <c r="AF83">
+        <v>29</v>
+      </c>
+      <c r="AH83">
+        <v>4267</v>
+      </c>
+      <c r="AI83">
+        <v>28</v>
+      </c>
     </row>
-    <row r="84" spans="2:29" x14ac:dyDescent="0.35">
+    <row r="84" spans="2:35" x14ac:dyDescent="0.35">
       <c r="C84" t="s">
         <v>2</v>
       </c>
@@ -15633,6 +20007,8 @@
       <c r="K84">
         <v>19</v>
       </c>
+      <c r="L84" s="2"/>
+      <c r="M84" s="2"/>
       <c r="O84" t="s">
         <v>2</v>
       </c>
@@ -15654,6 +20030,8 @@
       <c r="W84">
         <v>10</v>
       </c>
+      <c r="X84" s="3"/>
+      <c r="Y84" s="3"/>
       <c r="AA84" t="s">
         <v>2</v>
       </c>
@@ -15663,8 +20041,20 @@
       <c r="AC84">
         <v>30</v>
       </c>
+      <c r="AE84">
+        <v>4129</v>
+      </c>
+      <c r="AF84">
+        <v>28</v>
+      </c>
+      <c r="AH84">
+        <v>4371</v>
+      </c>
+      <c r="AI84">
+        <v>27</v>
+      </c>
     </row>
-    <row r="85" spans="2:29" x14ac:dyDescent="0.35">
+    <row r="85" spans="2:35" x14ac:dyDescent="0.35">
       <c r="C85" t="s">
         <v>3</v>
       </c>
@@ -15686,6 +20076,8 @@
       <c r="K85">
         <v>20</v>
       </c>
+      <c r="L85" s="2"/>
+      <c r="M85" s="2"/>
       <c r="O85" t="s">
         <v>3</v>
       </c>
@@ -15707,6 +20099,8 @@
       <c r="W85">
         <v>9</v>
       </c>
+      <c r="X85" s="3"/>
+      <c r="Y85" s="3"/>
       <c r="AA85" t="s">
         <v>3</v>
       </c>
@@ -15716,8 +20110,20 @@
       <c r="AC85">
         <v>27</v>
       </c>
+      <c r="AE85">
+        <v>4252</v>
+      </c>
+      <c r="AF85">
+        <v>27</v>
+      </c>
+      <c r="AH85">
+        <v>4456</v>
+      </c>
+      <c r="AI85">
+        <v>28</v>
+      </c>
     </row>
-    <row r="86" spans="2:29" x14ac:dyDescent="0.35">
+    <row r="86" spans="2:35" x14ac:dyDescent="0.35">
       <c r="C86" t="s">
         <v>4</v>
       </c>
@@ -15739,6 +20145,8 @@
       <c r="K86">
         <v>19</v>
       </c>
+      <c r="L86" s="2"/>
+      <c r="M86" s="2"/>
       <c r="O86" t="s">
         <v>4</v>
       </c>
@@ -15760,6 +20168,8 @@
       <c r="W86">
         <v>4</v>
       </c>
+      <c r="X86" s="3"/>
+      <c r="Y86" s="3"/>
       <c r="AA86" t="s">
         <v>4</v>
       </c>
@@ -15769,8 +20179,20 @@
       <c r="AC86">
         <v>30</v>
       </c>
+      <c r="AE86">
+        <v>4356</v>
+      </c>
+      <c r="AF86">
+        <v>28</v>
+      </c>
+      <c r="AH86">
+        <v>4467</v>
+      </c>
+      <c r="AI86">
+        <v>30</v>
+      </c>
     </row>
-    <row r="87" spans="2:29" x14ac:dyDescent="0.35">
+    <row r="87" spans="2:35" x14ac:dyDescent="0.35">
       <c r="C87" t="s">
         <v>5</v>
       </c>
@@ -15792,6 +20214,8 @@
       <c r="K87">
         <v>20</v>
       </c>
+      <c r="L87" s="2"/>
+      <c r="M87" s="2"/>
       <c r="O87" t="s">
         <v>5</v>
       </c>
@@ -15813,6 +20237,8 @@
       <c r="W87">
         <v>12</v>
       </c>
+      <c r="X87" s="3"/>
+      <c r="Y87" s="3"/>
       <c r="AA87" t="s">
         <v>5</v>
       </c>
@@ -15822,19 +20248,35 @@
       <c r="AC87">
         <v>29</v>
       </c>
+      <c r="AE87">
+        <v>4140</v>
+      </c>
+      <c r="AF87">
+        <v>30</v>
+      </c>
+      <c r="AH87">
+        <v>4400</v>
+      </c>
+      <c r="AI87">
+        <v>29</v>
+      </c>
     </row>
-    <row r="88" spans="2:29" x14ac:dyDescent="0.35">
+    <row r="88" spans="2:35" x14ac:dyDescent="0.35">
       <c r="B88" t="s">
         <v>19</v>
       </c>
+      <c r="L88" s="2"/>
+      <c r="M88" s="2"/>
       <c r="N88" t="s">
         <v>19</v>
       </c>
+      <c r="X88" s="3"/>
+      <c r="Y88" s="3"/>
       <c r="Z88" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="89" spans="2:29" x14ac:dyDescent="0.35">
+    <row r="89" spans="2:35" x14ac:dyDescent="0.35">
       <c r="C89" t="s">
         <v>1</v>
       </c>
@@ -15856,6 +20298,8 @@
       <c r="K89">
         <v>15</v>
       </c>
+      <c r="L89" s="2"/>
+      <c r="M89" s="2"/>
       <c r="O89" t="s">
         <v>1</v>
       </c>
@@ -15877,6 +20321,8 @@
       <c r="W89">
         <v>8</v>
       </c>
+      <c r="X89" s="3"/>
+      <c r="Y89" s="3"/>
       <c r="AA89" t="s">
         <v>1</v>
       </c>
@@ -15886,8 +20332,20 @@
       <c r="AC89">
         <v>30</v>
       </c>
+      <c r="AE89">
+        <v>4065</v>
+      </c>
+      <c r="AF89">
+        <v>28</v>
+      </c>
+      <c r="AH89">
+        <v>4528</v>
+      </c>
+      <c r="AI89">
+        <v>30</v>
+      </c>
     </row>
-    <row r="90" spans="2:29" x14ac:dyDescent="0.35">
+    <row r="90" spans="2:35" x14ac:dyDescent="0.35">
       <c r="C90" t="s">
         <v>2</v>
       </c>
@@ -15909,6 +20367,8 @@
       <c r="K90">
         <v>17</v>
       </c>
+      <c r="L90" s="2"/>
+      <c r="M90" s="2"/>
       <c r="O90" t="s">
         <v>2</v>
       </c>
@@ -15930,6 +20390,8 @@
       <c r="W90">
         <v>13</v>
       </c>
+      <c r="X90" s="3"/>
+      <c r="Y90" s="3"/>
       <c r="AA90" t="s">
         <v>2</v>
       </c>
@@ -15939,8 +20401,20 @@
       <c r="AC90">
         <v>28</v>
       </c>
+      <c r="AE90">
+        <v>4045</v>
+      </c>
+      <c r="AF90">
+        <v>29</v>
+      </c>
+      <c r="AH90">
+        <v>4440</v>
+      </c>
+      <c r="AI90">
+        <v>30</v>
+      </c>
     </row>
-    <row r="91" spans="2:29" x14ac:dyDescent="0.35">
+    <row r="91" spans="2:35" x14ac:dyDescent="0.35">
       <c r="C91" t="s">
         <v>3</v>
       </c>
@@ -15962,6 +20436,8 @@
       <c r="K91">
         <v>19</v>
       </c>
+      <c r="L91" s="2"/>
+      <c r="M91" s="2"/>
       <c r="O91" t="s">
         <v>3</v>
       </c>
@@ -15983,6 +20459,8 @@
       <c r="W91">
         <v>11</v>
       </c>
+      <c r="X91" s="3"/>
+      <c r="Y91" s="3"/>
       <c r="AA91" t="s">
         <v>3</v>
       </c>
@@ -15992,8 +20470,20 @@
       <c r="AC91">
         <v>28</v>
       </c>
+      <c r="AE91">
+        <v>4102</v>
+      </c>
+      <c r="AF91">
+        <v>30</v>
+      </c>
+      <c r="AH91">
+        <v>4329</v>
+      </c>
+      <c r="AI91">
+        <v>29</v>
+      </c>
     </row>
-    <row r="92" spans="2:29" x14ac:dyDescent="0.35">
+    <row r="92" spans="2:35" x14ac:dyDescent="0.35">
       <c r="C92" t="s">
         <v>4</v>
       </c>
@@ -16015,6 +20505,8 @@
       <c r="K92">
         <v>19</v>
       </c>
+      <c r="L92" s="2"/>
+      <c r="M92" s="2"/>
       <c r="O92" t="s">
         <v>4</v>
       </c>
@@ -16036,6 +20528,8 @@
       <c r="W92">
         <v>5</v>
       </c>
+      <c r="X92" s="3"/>
+      <c r="Y92" s="3"/>
       <c r="AA92" t="s">
         <v>4</v>
       </c>
@@ -16045,8 +20539,20 @@
       <c r="AC92">
         <v>28</v>
       </c>
+      <c r="AE92">
+        <v>4166</v>
+      </c>
+      <c r="AF92">
+        <v>29</v>
+      </c>
+      <c r="AH92">
+        <v>4317</v>
+      </c>
+      <c r="AI92">
+        <v>29</v>
+      </c>
     </row>
-    <row r="93" spans="2:29" x14ac:dyDescent="0.35">
+    <row r="93" spans="2:35" x14ac:dyDescent="0.35">
       <c r="C93" t="s">
         <v>5</v>
       </c>
@@ -16068,6 +20574,8 @@
       <c r="K93">
         <v>17</v>
       </c>
+      <c r="L93" s="2"/>
+      <c r="M93" s="2"/>
       <c r="O93" t="s">
         <v>5</v>
       </c>
@@ -16089,6 +20597,8 @@
       <c r="W93">
         <v>10</v>
       </c>
+      <c r="X93" s="3"/>
+      <c r="Y93" s="3"/>
       <c r="AA93" t="s">
         <v>5</v>
       </c>
@@ -16098,19 +20608,35 @@
       <c r="AC93">
         <v>28</v>
       </c>
+      <c r="AE93">
+        <v>4188</v>
+      </c>
+      <c r="AF93">
+        <v>28</v>
+      </c>
+      <c r="AH93">
+        <v>4342</v>
+      </c>
+      <c r="AI93">
+        <v>29</v>
+      </c>
     </row>
-    <row r="94" spans="2:29" x14ac:dyDescent="0.35">
+    <row r="94" spans="2:35" x14ac:dyDescent="0.35">
       <c r="B94" t="s">
         <v>20</v>
       </c>
+      <c r="L94" s="2"/>
+      <c r="M94" s="2"/>
       <c r="N94" t="s">
         <v>20</v>
       </c>
+      <c r="X94" s="3"/>
+      <c r="Y94" s="3"/>
       <c r="Z94" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="95" spans="2:29" x14ac:dyDescent="0.35">
+    <row r="95" spans="2:35" x14ac:dyDescent="0.35">
       <c r="C95" t="s">
         <v>1</v>
       </c>
@@ -16132,6 +20658,8 @@
       <c r="K95">
         <v>16</v>
       </c>
+      <c r="L95" s="2"/>
+      <c r="M95" s="2"/>
       <c r="O95" t="s">
         <v>1</v>
       </c>
@@ -16153,6 +20681,8 @@
       <c r="W95">
         <v>7</v>
       </c>
+      <c r="X95" s="3"/>
+      <c r="Y95" s="3"/>
       <c r="AA95" t="s">
         <v>1</v>
       </c>
@@ -16162,8 +20692,20 @@
       <c r="AC95">
         <v>30</v>
       </c>
+      <c r="AE95">
+        <v>4008</v>
+      </c>
+      <c r="AF95">
+        <v>27</v>
+      </c>
+      <c r="AH95">
+        <v>4436</v>
+      </c>
+      <c r="AI95">
+        <v>29</v>
+      </c>
     </row>
-    <row r="96" spans="2:29" x14ac:dyDescent="0.35">
+    <row r="96" spans="2:35" x14ac:dyDescent="0.35">
       <c r="C96" t="s">
         <v>2</v>
       </c>
@@ -16185,6 +20727,8 @@
       <c r="K96">
         <v>19</v>
       </c>
+      <c r="L96" s="2"/>
+      <c r="M96" s="2"/>
       <c r="O96" t="s">
         <v>2</v>
       </c>
@@ -16206,6 +20750,8 @@
       <c r="W96">
         <v>13</v>
       </c>
+      <c r="X96" s="3"/>
+      <c r="Y96" s="3"/>
       <c r="AA96" t="s">
         <v>2</v>
       </c>
@@ -16215,8 +20761,20 @@
       <c r="AC96">
         <v>29</v>
       </c>
+      <c r="AE96">
+        <v>3983</v>
+      </c>
+      <c r="AF96">
+        <v>29</v>
+      </c>
+      <c r="AH96">
+        <v>4419</v>
+      </c>
+      <c r="AI96">
+        <v>30</v>
+      </c>
     </row>
-    <row r="97" spans="2:29" x14ac:dyDescent="0.35">
+    <row r="97" spans="2:35" x14ac:dyDescent="0.35">
       <c r="C97" t="s">
         <v>3</v>
       </c>
@@ -16238,6 +20796,8 @@
       <c r="K97">
         <v>20</v>
       </c>
+      <c r="L97" s="2"/>
+      <c r="M97" s="2"/>
       <c r="O97" t="s">
         <v>3</v>
       </c>
@@ -16259,6 +20819,8 @@
       <c r="W97">
         <v>11</v>
       </c>
+      <c r="X97" s="3"/>
+      <c r="Y97" s="3"/>
       <c r="AA97" t="s">
         <v>3</v>
       </c>
@@ -16268,8 +20830,20 @@
       <c r="AC97">
         <v>29</v>
       </c>
+      <c r="AE97">
+        <v>3973</v>
+      </c>
+      <c r="AF97">
+        <v>29</v>
+      </c>
+      <c r="AH97">
+        <v>4440</v>
+      </c>
+      <c r="AI97">
+        <v>26</v>
+      </c>
     </row>
-    <row r="98" spans="2:29" x14ac:dyDescent="0.35">
+    <row r="98" spans="2:35" x14ac:dyDescent="0.35">
       <c r="C98" t="s">
         <v>4</v>
       </c>
@@ -16291,6 +20865,8 @@
       <c r="K98">
         <v>21</v>
       </c>
+      <c r="L98" s="2"/>
+      <c r="M98" s="2"/>
       <c r="O98" t="s">
         <v>4</v>
       </c>
@@ -16312,6 +20888,8 @@
       <c r="W98">
         <v>9</v>
       </c>
+      <c r="X98" s="3"/>
+      <c r="Y98" s="3"/>
       <c r="AA98" t="s">
         <v>4</v>
       </c>
@@ -16321,8 +20899,20 @@
       <c r="AC98">
         <v>26</v>
       </c>
+      <c r="AE98">
+        <v>3993</v>
+      </c>
+      <c r="AF98">
+        <v>30</v>
+      </c>
+      <c r="AH98">
+        <v>4321</v>
+      </c>
+      <c r="AI98">
+        <v>28</v>
+      </c>
     </row>
-    <row r="99" spans="2:29" x14ac:dyDescent="0.35">
+    <row r="99" spans="2:35" x14ac:dyDescent="0.35">
       <c r="C99" t="s">
         <v>5</v>
       </c>
@@ -16344,6 +20934,8 @@
       <c r="K99">
         <v>20</v>
       </c>
+      <c r="L99" s="2"/>
+      <c r="M99" s="2"/>
       <c r="O99" t="s">
         <v>5</v>
       </c>
@@ -16365,6 +20957,8 @@
       <c r="W99">
         <v>9</v>
       </c>
+      <c r="X99" s="3"/>
+      <c r="Y99" s="3"/>
       <c r="AA99" t="s">
         <v>5</v>
       </c>
@@ -16374,19 +20968,35 @@
       <c r="AC99">
         <v>28</v>
       </c>
+      <c r="AE99">
+        <v>3966</v>
+      </c>
+      <c r="AF99">
+        <v>29</v>
+      </c>
+      <c r="AH99">
+        <v>4322</v>
+      </c>
+      <c r="AI99">
+        <v>28</v>
+      </c>
     </row>
-    <row r="100" spans="2:29" x14ac:dyDescent="0.35">
+    <row r="100" spans="2:35" x14ac:dyDescent="0.35">
       <c r="B100" t="s">
         <v>21</v>
       </c>
+      <c r="L100" s="2"/>
+      <c r="M100" s="2"/>
       <c r="N100" t="s">
         <v>21</v>
       </c>
+      <c r="X100" s="3"/>
+      <c r="Y100" s="3"/>
       <c r="Z100" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="101" spans="2:29" x14ac:dyDescent="0.35">
+    <row r="101" spans="2:35" x14ac:dyDescent="0.35">
       <c r="C101" t="s">
         <v>1</v>
       </c>
@@ -16408,6 +21018,8 @@
       <c r="K101">
         <v>15</v>
       </c>
+      <c r="L101" s="2"/>
+      <c r="M101" s="2"/>
       <c r="O101" t="s">
         <v>1</v>
       </c>
@@ -16429,6 +21041,8 @@
       <c r="W101">
         <v>11</v>
       </c>
+      <c r="X101" s="3"/>
+      <c r="Y101" s="3"/>
       <c r="AA101" t="s">
         <v>1</v>
       </c>
@@ -16438,8 +21052,20 @@
       <c r="AC101">
         <v>29</v>
       </c>
+      <c r="AE101">
+        <v>4052</v>
+      </c>
+      <c r="AF101">
+        <v>28</v>
+      </c>
+      <c r="AH101">
+        <v>4407</v>
+      </c>
+      <c r="AI101">
+        <v>27</v>
+      </c>
     </row>
-    <row r="102" spans="2:29" x14ac:dyDescent="0.35">
+    <row r="102" spans="2:35" x14ac:dyDescent="0.35">
       <c r="C102" t="s">
         <v>2</v>
       </c>
@@ -16461,6 +21087,8 @@
       <c r="K102">
         <v>10</v>
       </c>
+      <c r="L102" s="2"/>
+      <c r="M102" s="2"/>
       <c r="O102" t="s">
         <v>2</v>
       </c>
@@ -16482,6 +21110,8 @@
       <c r="W102">
         <v>10</v>
       </c>
+      <c r="X102" s="3"/>
+      <c r="Y102" s="3"/>
       <c r="AA102" t="s">
         <v>2</v>
       </c>
@@ -16491,8 +21121,20 @@
       <c r="AC102">
         <v>27</v>
       </c>
+      <c r="AE102">
+        <v>4055</v>
+      </c>
+      <c r="AF102">
+        <v>27</v>
+      </c>
+      <c r="AH102">
+        <v>4374</v>
+      </c>
+      <c r="AI102">
+        <v>29</v>
+      </c>
     </row>
-    <row r="103" spans="2:29" x14ac:dyDescent="0.35">
+    <row r="103" spans="2:35" x14ac:dyDescent="0.35">
       <c r="C103" t="s">
         <v>3</v>
       </c>
@@ -16514,6 +21156,8 @@
       <c r="K103">
         <v>17</v>
       </c>
+      <c r="L103" s="2"/>
+      <c r="M103" s="2"/>
       <c r="O103" t="s">
         <v>3</v>
       </c>
@@ -16535,6 +21179,8 @@
       <c r="W103">
         <v>6</v>
       </c>
+      <c r="X103" s="3"/>
+      <c r="Y103" s="3"/>
       <c r="AA103" t="s">
         <v>3</v>
       </c>
@@ -16544,8 +21190,20 @@
       <c r="AC103">
         <v>29</v>
       </c>
+      <c r="AE103">
+        <v>4040</v>
+      </c>
+      <c r="AF103">
+        <v>28</v>
+      </c>
+      <c r="AH103">
+        <v>4303</v>
+      </c>
+      <c r="AI103">
+        <v>30</v>
+      </c>
     </row>
-    <row r="104" spans="2:29" x14ac:dyDescent="0.35">
+    <row r="104" spans="2:35" x14ac:dyDescent="0.35">
       <c r="C104" t="s">
         <v>4</v>
       </c>
@@ -16567,6 +21225,8 @@
       <c r="K104">
         <v>15</v>
       </c>
+      <c r="L104" s="2"/>
+      <c r="M104" s="2"/>
       <c r="O104" t="s">
         <v>4</v>
       </c>
@@ -16588,6 +21248,8 @@
       <c r="W104">
         <v>11</v>
       </c>
+      <c r="X104" s="3"/>
+      <c r="Y104" s="3"/>
       <c r="AA104" t="s">
         <v>4</v>
       </c>
@@ -16597,8 +21259,20 @@
       <c r="AC104">
         <v>27</v>
       </c>
+      <c r="AE104">
+        <v>4038</v>
+      </c>
+      <c r="AF104">
+        <v>29</v>
+      </c>
+      <c r="AH104">
+        <v>4263</v>
+      </c>
+      <c r="AI104">
+        <v>27</v>
+      </c>
     </row>
-    <row r="105" spans="2:29" x14ac:dyDescent="0.35">
+    <row r="105" spans="2:35" x14ac:dyDescent="0.35">
       <c r="C105" t="s">
         <v>5</v>
       </c>
@@ -16620,6 +21294,8 @@
       <c r="K105">
         <v>14</v>
       </c>
+      <c r="L105" s="2"/>
+      <c r="M105" s="2"/>
       <c r="O105" t="s">
         <v>5</v>
       </c>
@@ -16641,6 +21317,8 @@
       <c r="W105">
         <v>8</v>
       </c>
+      <c r="X105" s="3"/>
+      <c r="Y105" s="3"/>
       <c r="AA105" t="s">
         <v>5</v>
       </c>
@@ -16650,19 +21328,35 @@
       <c r="AC105">
         <v>27</v>
       </c>
+      <c r="AE105">
+        <v>4076</v>
+      </c>
+      <c r="AF105">
+        <v>23</v>
+      </c>
+      <c r="AH105">
+        <v>4302</v>
+      </c>
+      <c r="AI105">
+        <v>30</v>
+      </c>
     </row>
-    <row r="106" spans="2:29" x14ac:dyDescent="0.35">
+    <row r="106" spans="2:35" x14ac:dyDescent="0.35">
       <c r="B106" t="s">
         <v>22</v>
       </c>
+      <c r="L106" s="2"/>
+      <c r="M106" s="2"/>
       <c r="N106" t="s">
         <v>22</v>
       </c>
+      <c r="X106" s="3"/>
+      <c r="Y106" s="3"/>
       <c r="Z106" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="107" spans="2:29" x14ac:dyDescent="0.35">
+    <row r="107" spans="2:35" x14ac:dyDescent="0.35">
       <c r="C107" t="s">
         <v>1</v>
       </c>
@@ -16684,6 +21378,8 @@
       <c r="K107">
         <v>19</v>
       </c>
+      <c r="L107" s="2"/>
+      <c r="M107" s="2"/>
       <c r="O107" t="s">
         <v>1</v>
       </c>
@@ -16705,6 +21401,8 @@
       <c r="W107">
         <v>10</v>
       </c>
+      <c r="X107" s="3"/>
+      <c r="Y107" s="3"/>
       <c r="AA107" t="s">
         <v>1</v>
       </c>
@@ -16714,8 +21412,20 @@
       <c r="AC107">
         <v>29</v>
       </c>
+      <c r="AE107">
+        <v>3965</v>
+      </c>
+      <c r="AF107">
+        <v>29</v>
+      </c>
+      <c r="AH107">
+        <v>4296</v>
+      </c>
+      <c r="AI107">
+        <v>27</v>
+      </c>
     </row>
-    <row r="108" spans="2:29" x14ac:dyDescent="0.35">
+    <row r="108" spans="2:35" x14ac:dyDescent="0.35">
       <c r="C108" t="s">
         <v>2</v>
       </c>
@@ -16737,6 +21447,8 @@
       <c r="K108">
         <v>16</v>
       </c>
+      <c r="L108" s="2"/>
+      <c r="M108" s="2"/>
       <c r="O108" t="s">
         <v>2</v>
       </c>
@@ -16758,6 +21470,8 @@
       <c r="W108">
         <v>10</v>
       </c>
+      <c r="X108" s="3"/>
+      <c r="Y108" s="3"/>
       <c r="AA108" t="s">
         <v>2</v>
       </c>
@@ -16767,8 +21481,20 @@
       <c r="AC108">
         <v>26</v>
       </c>
+      <c r="AE108">
+        <v>3966</v>
+      </c>
+      <c r="AF108">
+        <v>29</v>
+      </c>
+      <c r="AH108">
+        <v>4336</v>
+      </c>
+      <c r="AI108">
+        <v>28</v>
+      </c>
     </row>
-    <row r="109" spans="2:29" x14ac:dyDescent="0.35">
+    <row r="109" spans="2:35" x14ac:dyDescent="0.35">
       <c r="C109" t="s">
         <v>3</v>
       </c>
@@ -16790,6 +21516,8 @@
       <c r="K109">
         <v>21</v>
       </c>
+      <c r="L109" s="2"/>
+      <c r="M109" s="2"/>
       <c r="O109" t="s">
         <v>3</v>
       </c>
@@ -16811,6 +21539,8 @@
       <c r="W109">
         <v>8</v>
       </c>
+      <c r="X109" s="3"/>
+      <c r="Y109" s="3"/>
       <c r="AA109" t="s">
         <v>3</v>
       </c>
@@ -16820,8 +21550,20 @@
       <c r="AC109">
         <v>28</v>
       </c>
+      <c r="AE109">
+        <v>3960</v>
+      </c>
+      <c r="AF109">
+        <v>30</v>
+      </c>
+      <c r="AH109">
+        <v>4219</v>
+      </c>
+      <c r="AI109">
+        <v>29</v>
+      </c>
     </row>
-    <row r="110" spans="2:29" x14ac:dyDescent="0.35">
+    <row r="110" spans="2:35" x14ac:dyDescent="0.35">
       <c r="C110" t="s">
         <v>4</v>
       </c>
@@ -16843,6 +21585,8 @@
       <c r="K110">
         <v>14</v>
       </c>
+      <c r="L110" s="2"/>
+      <c r="M110" s="2"/>
       <c r="O110" t="s">
         <v>4</v>
       </c>
@@ -16864,6 +21608,8 @@
       <c r="W110">
         <v>8</v>
       </c>
+      <c r="X110" s="3"/>
+      <c r="Y110" s="3"/>
       <c r="AA110" t="s">
         <v>4</v>
       </c>
@@ -16873,8 +21619,20 @@
       <c r="AC110">
         <v>29</v>
       </c>
+      <c r="AE110">
+        <v>3954</v>
+      </c>
+      <c r="AF110">
+        <v>28</v>
+      </c>
+      <c r="AH110">
+        <v>3994</v>
+      </c>
+      <c r="AI110">
+        <v>28</v>
+      </c>
     </row>
-    <row r="111" spans="2:29" x14ac:dyDescent="0.35">
+    <row r="111" spans="2:35" x14ac:dyDescent="0.35">
       <c r="C111" t="s">
         <v>5</v>
       </c>
@@ -16896,6 +21654,8 @@
       <c r="K111">
         <v>20</v>
       </c>
+      <c r="L111" s="2"/>
+      <c r="M111" s="2"/>
       <c r="O111" t="s">
         <v>5</v>
       </c>
@@ -16917,6 +21677,8 @@
       <c r="W111">
         <v>10</v>
       </c>
+      <c r="X111" s="3"/>
+      <c r="Y111" s="3"/>
       <c r="AA111" t="s">
         <v>5</v>
       </c>
@@ -16926,19 +21688,35 @@
       <c r="AC111">
         <v>29</v>
       </c>
+      <c r="AE111">
+        <v>3990</v>
+      </c>
+      <c r="AF111">
+        <v>27</v>
+      </c>
+      <c r="AH111">
+        <v>4022</v>
+      </c>
+      <c r="AI111">
+        <v>27</v>
+      </c>
     </row>
-    <row r="112" spans="2:29" x14ac:dyDescent="0.35">
+    <row r="112" spans="2:35" x14ac:dyDescent="0.35">
       <c r="B112" t="s">
         <v>23</v>
       </c>
+      <c r="L112" s="2"/>
+      <c r="M112" s="2"/>
       <c r="N112" t="s">
         <v>23</v>
       </c>
+      <c r="X112" s="3"/>
+      <c r="Y112" s="3"/>
       <c r="Z112" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="113" spans="2:29" x14ac:dyDescent="0.35">
+    <row r="113" spans="2:35" x14ac:dyDescent="0.35">
       <c r="C113" t="s">
         <v>1</v>
       </c>
@@ -16960,6 +21738,8 @@
       <c r="K113">
         <v>18</v>
       </c>
+      <c r="L113" s="2"/>
+      <c r="M113" s="2"/>
       <c r="O113" t="s">
         <v>1</v>
       </c>
@@ -16981,6 +21761,8 @@
       <c r="W113">
         <v>9</v>
       </c>
+      <c r="X113" s="3"/>
+      <c r="Y113" s="3"/>
       <c r="AA113" t="s">
         <v>1</v>
       </c>
@@ -16990,8 +21772,20 @@
       <c r="AC113">
         <v>29</v>
       </c>
+      <c r="AE113">
+        <v>4106</v>
+      </c>
+      <c r="AF113">
+        <v>29</v>
+      </c>
+      <c r="AH113">
+        <v>4228</v>
+      </c>
+      <c r="AI113">
+        <v>26</v>
+      </c>
     </row>
-    <row r="114" spans="2:29" x14ac:dyDescent="0.35">
+    <row r="114" spans="2:35" x14ac:dyDescent="0.35">
       <c r="C114" t="s">
         <v>2</v>
       </c>
@@ -17013,6 +21807,8 @@
       <c r="K114">
         <v>22</v>
       </c>
+      <c r="L114" s="2"/>
+      <c r="M114" s="2"/>
       <c r="O114" t="s">
         <v>2</v>
       </c>
@@ -17034,6 +21830,8 @@
       <c r="W114">
         <v>7</v>
       </c>
+      <c r="X114" s="3"/>
+      <c r="Y114" s="3"/>
       <c r="AA114" t="s">
         <v>2</v>
       </c>
@@ -17043,8 +21841,20 @@
       <c r="AC114">
         <v>28</v>
       </c>
+      <c r="AE114">
+        <v>4084</v>
+      </c>
+      <c r="AF114">
+        <v>29</v>
+      </c>
+      <c r="AH114">
+        <v>4323</v>
+      </c>
+      <c r="AI114">
+        <v>26</v>
+      </c>
     </row>
-    <row r="115" spans="2:29" x14ac:dyDescent="0.35">
+    <row r="115" spans="2:35" x14ac:dyDescent="0.35">
       <c r="C115" t="s">
         <v>3</v>
       </c>
@@ -17066,6 +21876,8 @@
       <c r="K115">
         <v>22</v>
       </c>
+      <c r="L115" s="2"/>
+      <c r="M115" s="2"/>
       <c r="O115" t="s">
         <v>3</v>
       </c>
@@ -17087,6 +21899,8 @@
       <c r="W115">
         <v>13</v>
       </c>
+      <c r="X115" s="3"/>
+      <c r="Y115" s="3"/>
       <c r="AA115" t="s">
         <v>3</v>
       </c>
@@ -17096,8 +21910,20 @@
       <c r="AC115">
         <v>25</v>
       </c>
+      <c r="AE115">
+        <v>4006</v>
+      </c>
+      <c r="AF115">
+        <v>28</v>
+      </c>
+      <c r="AH115">
+        <v>4261</v>
+      </c>
+      <c r="AI115">
+        <v>28</v>
+      </c>
     </row>
-    <row r="116" spans="2:29" x14ac:dyDescent="0.35">
+    <row r="116" spans="2:35" x14ac:dyDescent="0.35">
       <c r="C116" t="s">
         <v>4</v>
       </c>
@@ -17119,6 +21945,8 @@
       <c r="K116">
         <v>22</v>
       </c>
+      <c r="L116" s="2"/>
+      <c r="M116" s="2"/>
       <c r="O116" t="s">
         <v>4</v>
       </c>
@@ -17140,6 +21968,8 @@
       <c r="W116">
         <v>10</v>
       </c>
+      <c r="X116" s="3"/>
+      <c r="Y116" s="3"/>
       <c r="AA116" t="s">
         <v>4</v>
       </c>
@@ -17149,8 +21979,20 @@
       <c r="AC116">
         <v>30</v>
       </c>
+      <c r="AE116">
+        <v>4062</v>
+      </c>
+      <c r="AF116">
+        <v>28</v>
+      </c>
+      <c r="AH116">
+        <v>4310</v>
+      </c>
+      <c r="AI116">
+        <v>29</v>
+      </c>
     </row>
-    <row r="117" spans="2:29" x14ac:dyDescent="0.35">
+    <row r="117" spans="2:35" x14ac:dyDescent="0.35">
       <c r="C117" t="s">
         <v>5</v>
       </c>
@@ -17172,6 +22014,8 @@
       <c r="K117">
         <v>22</v>
       </c>
+      <c r="L117" s="2"/>
+      <c r="M117" s="2"/>
       <c r="O117" t="s">
         <v>5</v>
       </c>
@@ -17193,6 +22037,8 @@
       <c r="W117">
         <v>9</v>
       </c>
+      <c r="X117" s="3"/>
+      <c r="Y117" s="3"/>
       <c r="AA117" t="s">
         <v>5</v>
       </c>
@@ -17202,19 +22048,35 @@
       <c r="AC117">
         <v>25</v>
       </c>
+      <c r="AE117">
+        <v>4091</v>
+      </c>
+      <c r="AF117">
+        <v>28</v>
+      </c>
+      <c r="AH117">
+        <v>4329</v>
+      </c>
+      <c r="AI117">
+        <v>26</v>
+      </c>
     </row>
-    <row r="118" spans="2:29" x14ac:dyDescent="0.35">
+    <row r="118" spans="2:35" x14ac:dyDescent="0.35">
       <c r="B118" t="s">
         <v>24</v>
       </c>
+      <c r="L118" s="2"/>
+      <c r="M118" s="2"/>
       <c r="N118" t="s">
         <v>24</v>
       </c>
+      <c r="X118" s="3"/>
+      <c r="Y118" s="3"/>
       <c r="Z118" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="119" spans="2:29" x14ac:dyDescent="0.35">
+    <row r="119" spans="2:35" x14ac:dyDescent="0.35">
       <c r="C119" t="s">
         <v>1</v>
       </c>
@@ -17236,6 +22098,8 @@
       <c r="K119">
         <v>17</v>
       </c>
+      <c r="L119" s="2"/>
+      <c r="M119" s="2"/>
       <c r="O119" t="s">
         <v>1</v>
       </c>
@@ -17257,6 +22121,8 @@
       <c r="W119">
         <v>4</v>
       </c>
+      <c r="X119" s="3"/>
+      <c r="Y119" s="3"/>
       <c r="AA119" t="s">
         <v>1</v>
       </c>
@@ -17266,8 +22132,20 @@
       <c r="AC119">
         <v>29</v>
       </c>
+      <c r="AE119">
+        <v>4031</v>
+      </c>
+      <c r="AF119">
+        <v>28</v>
+      </c>
+      <c r="AH119">
+        <v>4447</v>
+      </c>
+      <c r="AI119">
+        <v>30</v>
+      </c>
     </row>
-    <row r="120" spans="2:29" x14ac:dyDescent="0.35">
+    <row r="120" spans="2:35" x14ac:dyDescent="0.35">
       <c r="C120" t="s">
         <v>2</v>
       </c>
@@ -17289,6 +22167,8 @@
       <c r="K120">
         <v>17</v>
       </c>
+      <c r="L120" s="2"/>
+      <c r="M120" s="2"/>
       <c r="O120" t="s">
         <v>2</v>
       </c>
@@ -17310,6 +22190,8 @@
       <c r="W120">
         <v>5</v>
       </c>
+      <c r="X120" s="3"/>
+      <c r="Y120" s="3"/>
       <c r="AA120" t="s">
         <v>2</v>
       </c>
@@ -17319,8 +22201,20 @@
       <c r="AC120">
         <v>30</v>
       </c>
+      <c r="AE120">
+        <v>4010</v>
+      </c>
+      <c r="AF120">
+        <v>27</v>
+      </c>
+      <c r="AH120">
+        <v>4518</v>
+      </c>
+      <c r="AI120">
+        <v>27</v>
+      </c>
     </row>
-    <row r="121" spans="2:29" x14ac:dyDescent="0.35">
+    <row r="121" spans="2:35" x14ac:dyDescent="0.35">
       <c r="C121" t="s">
         <v>3</v>
       </c>
@@ -17342,6 +22236,8 @@
       <c r="K121">
         <v>19</v>
       </c>
+      <c r="L121" s="2"/>
+      <c r="M121" s="2"/>
       <c r="O121" t="s">
         <v>3</v>
       </c>
@@ -17363,6 +22259,8 @@
       <c r="W121">
         <v>15</v>
       </c>
+      <c r="X121" s="3"/>
+      <c r="Y121" s="3"/>
       <c r="AA121" t="s">
         <v>3</v>
       </c>
@@ -17372,8 +22270,20 @@
       <c r="AC121">
         <v>29</v>
       </c>
+      <c r="AE121">
+        <v>4038</v>
+      </c>
+      <c r="AF121">
+        <v>26</v>
+      </c>
+      <c r="AH121">
+        <v>4262</v>
+      </c>
+      <c r="AI121">
+        <v>30</v>
+      </c>
     </row>
-    <row r="122" spans="2:29" x14ac:dyDescent="0.35">
+    <row r="122" spans="2:35" x14ac:dyDescent="0.35">
       <c r="C122" t="s">
         <v>4</v>
       </c>
@@ -17395,6 +22305,8 @@
       <c r="K122">
         <v>17</v>
       </c>
+      <c r="L122" s="2"/>
+      <c r="M122" s="2"/>
       <c r="O122" t="s">
         <v>4</v>
       </c>
@@ -17416,6 +22328,8 @@
       <c r="W122">
         <v>9</v>
       </c>
+      <c r="X122" s="3"/>
+      <c r="Y122" s="3"/>
       <c r="AA122" t="s">
         <v>4</v>
       </c>
@@ -17425,8 +22339,20 @@
       <c r="AC122">
         <v>30</v>
       </c>
+      <c r="AE122">
+        <v>4031</v>
+      </c>
+      <c r="AF122">
+        <v>29</v>
+      </c>
+      <c r="AH122">
+        <v>4352</v>
+      </c>
+      <c r="AI122">
+        <v>29</v>
+      </c>
     </row>
-    <row r="123" spans="2:29" x14ac:dyDescent="0.35">
+    <row r="123" spans="2:35" x14ac:dyDescent="0.35">
       <c r="C123" t="s">
         <v>5</v>
       </c>
@@ -17448,6 +22374,8 @@
       <c r="K123">
         <v>17</v>
       </c>
+      <c r="L123" s="2"/>
+      <c r="M123" s="2"/>
       <c r="O123" t="s">
         <v>5</v>
       </c>
@@ -17469,6 +22397,8 @@
       <c r="W123">
         <v>6</v>
       </c>
+      <c r="X123" s="3"/>
+      <c r="Y123" s="3"/>
       <c r="AA123" t="s">
         <v>5</v>
       </c>
@@ -17476,6 +22406,18 @@
         <v>4095</v>
       </c>
       <c r="AC123">
+        <v>29</v>
+      </c>
+      <c r="AE123">
+        <v>4025</v>
+      </c>
+      <c r="AF123">
+        <v>29</v>
+      </c>
+      <c r="AH123">
+        <v>4285</v>
+      </c>
+      <c r="AI123">
         <v>29</v>
       </c>
     </row>
